--- a/tri_county_data.xlsx
+++ b/tri_county_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1694"/>
+  <dimension ref="A1:F1695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39413,7 +39413,7 @@
       </c>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>Migrant Status</t>
+          <t>Grade Level</t>
         </is>
       </c>
       <c r="D1234" t="inlineStr">
@@ -39423,19 +39423,19 @@
       </c>
       <c r="E1234" t="inlineStr">
         <is>
-          <t>UNK9</t>
+          <t>UNK8</t>
         </is>
       </c>
       <c r="F1234" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1235">
       <c r="A1235" t="inlineStr">
         <is>
-          <t>Freedom Middle</t>
+          <t>Winneconne Middle</t>
         </is>
       </c>
       <c r="B1235" t="inlineStr">
@@ -39445,34 +39445,34 @@
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Race/Ethnicity</t>
+          <t>Migrant Status</t>
         </is>
       </c>
       <c r="D1235" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E1235" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>UNK9</t>
         </is>
       </c>
       <c r="F1235" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="1236">
       <c r="A1236" t="inlineStr">
         <is>
-          <t>Clovis Grove Elementary</t>
+          <t>Freedom Middle</t>
         </is>
       </c>
       <c r="B1236" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1236" t="inlineStr">
@@ -39499,7 +39499,7 @@
     <row r="1237">
       <c r="A1237" t="inlineStr">
         <is>
-          <t>Johnston Elementary</t>
+          <t>Edison Elementary</t>
         </is>
       </c>
       <c r="B1237" t="inlineStr">
@@ -39531,12 +39531,12 @@
     <row r="1238">
       <c r="A1238" t="inlineStr">
         <is>
-          <t>Taft Elementary</t>
+          <t>Greenville Elementary</t>
         </is>
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1238" t="inlineStr">
@@ -39556,19 +39556,19 @@
       </c>
       <c r="F1238" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="1239">
       <c r="A1239" t="inlineStr">
         <is>
-          <t>Wilson Middle</t>
+          <t>Butte des Morts Elementary</t>
         </is>
       </c>
       <c r="B1239" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1239" t="inlineStr">
@@ -39588,14 +39588,14 @@
       </c>
       <c r="F1239" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="1240">
       <c r="A1240" t="inlineStr">
         <is>
-          <t>Merrill Elementary</t>
+          <t>Traeger Middle</t>
         </is>
       </c>
       <c r="B1240" t="inlineStr">
@@ -39620,14 +39620,14 @@
       </c>
       <c r="F1240" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
-          <t>Fox West Academy</t>
+          <t>Einstein Middle</t>
         </is>
       </c>
       <c r="B1241" t="inlineStr">
@@ -39652,14 +39652,14 @@
       </c>
       <c r="F1241" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
         <is>
-          <t>Gegan Elementary</t>
+          <t>Taft Elementary</t>
         </is>
       </c>
       <c r="B1242" t="inlineStr">
@@ -39684,19 +39684,19 @@
       </c>
       <c r="F1242" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1243">
       <c r="A1243" t="inlineStr">
         <is>
-          <t>Einstein Middle</t>
+          <t>Washington Elementary</t>
         </is>
       </c>
       <c r="B1243" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1243" t="inlineStr">
@@ -39716,19 +39716,19 @@
       </c>
       <c r="F1243" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="1244">
       <c r="A1244" t="inlineStr">
         <is>
-          <t>Hilbert Middle</t>
+          <t>Wilson Middle</t>
         </is>
       </c>
       <c r="B1244" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1244" t="inlineStr">
@@ -39748,14 +39748,14 @@
       </c>
       <c r="F1244" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="1245">
       <c r="A1245" t="inlineStr">
         <is>
-          <t>Tipler Middle</t>
+          <t>Merrill Elementary</t>
         </is>
       </c>
       <c r="B1245" t="inlineStr">
@@ -39780,19 +39780,19 @@
       </c>
       <c r="F1245" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="1246">
       <c r="A1246" t="inlineStr">
         <is>
-          <t>Ferber Elementary</t>
+          <t>Clovis Grove Elementary</t>
         </is>
       </c>
       <c r="B1246" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1246" t="inlineStr">
@@ -39812,19 +39812,19 @@
       </c>
       <c r="F1246" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="1247">
       <c r="A1247" t="inlineStr">
         <is>
-          <t>Jefferson Elementary</t>
+          <t>Fox West Academy</t>
         </is>
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1247" t="inlineStr">
@@ -39844,19 +39844,19 @@
       </c>
       <c r="F1247" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1248">
       <c r="A1248" t="inlineStr">
         <is>
-          <t>Traeger Elementary</t>
+          <t>Johnston Elementary</t>
         </is>
       </c>
       <c r="B1248" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1248" t="inlineStr">
@@ -39876,19 +39876,19 @@
       </c>
       <c r="F1248" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1249">
       <c r="A1249" t="inlineStr">
         <is>
-          <t>Traeger Middle</t>
+          <t>Greenville Middle</t>
         </is>
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1249" t="inlineStr">
@@ -39908,19 +39908,19 @@
       </c>
       <c r="F1249" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="1250">
       <c r="A1250" t="inlineStr">
         <is>
-          <t>Greenville Elementary</t>
+          <t>Webster Stanley Elementary</t>
         </is>
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1250" t="inlineStr">
@@ -39940,19 +39940,19 @@
       </c>
       <c r="F1250" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
-          <t>Hilbert High</t>
+          <t>Traeger Elementary</t>
         </is>
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1251" t="inlineStr">
@@ -39972,19 +39972,19 @@
       </c>
       <c r="F1251" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="1252">
       <c r="A1252" t="inlineStr">
         <is>
-          <t>Edison Elementary</t>
+          <t>Tullar Elementary</t>
         </is>
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1252" t="inlineStr">
@@ -40004,19 +40004,19 @@
       </c>
       <c r="F1252" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="1253">
       <c r="A1253" t="inlineStr">
         <is>
-          <t>Washington Elementary</t>
+          <t>Little Chute Intermediate</t>
         </is>
       </c>
       <c r="B1253" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1253" t="inlineStr">
@@ -40036,14 +40036,14 @@
       </c>
       <c r="F1253" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="1254">
       <c r="A1254" t="inlineStr">
         <is>
-          <t>Greenville Middle</t>
+          <t>West High</t>
         </is>
       </c>
       <c r="B1254" t="inlineStr">
@@ -40068,14 +40068,14 @@
       </c>
       <c r="F1254" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="1255">
       <c r="A1255" t="inlineStr">
         <is>
-          <t>Little Chute Middle</t>
+          <t>Hortonville Elementary</t>
         </is>
       </c>
       <c r="B1255" t="inlineStr">
@@ -40100,19 +40100,19 @@
       </c>
       <c r="F1255" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1256">
       <c r="A1256" t="inlineStr">
         <is>
-          <t>Tullar Elementary</t>
+          <t>East High</t>
         </is>
       </c>
       <c r="B1256" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1256" t="inlineStr">
@@ -40132,14 +40132,14 @@
       </c>
       <c r="F1256" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>Webster Stanley Elementary</t>
+          <t>Lakeside Elementary</t>
         </is>
       </c>
       <c r="B1257" t="inlineStr">
@@ -40164,19 +40164,19 @@
       </c>
       <c r="F1257" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1258">
       <c r="A1258" t="inlineStr">
         <is>
-          <t>West High</t>
+          <t>Neenah High</t>
         </is>
       </c>
       <c r="B1258" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1258" t="inlineStr">
@@ -40196,19 +40196,19 @@
       </c>
       <c r="F1258" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>98</t>
         </is>
       </c>
     </row>
     <row r="1259">
       <c r="A1259" t="inlineStr">
         <is>
-          <t>Little Chute Intermediate</t>
+          <t>Webster Stanley Middle</t>
         </is>
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1259" t="inlineStr">
@@ -40228,14 +40228,14 @@
       </c>
       <c r="F1259" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="1260">
       <c r="A1260" t="inlineStr">
         <is>
-          <t>Hortonville Elementary</t>
+          <t>Little Chute High</t>
         </is>
       </c>
       <c r="B1260" t="inlineStr">
@@ -40260,14 +40260,14 @@
       </c>
       <c r="F1260" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
-          <t>East High</t>
+          <t>Kaleidoscope Academy</t>
         </is>
       </c>
       <c r="B1261" t="inlineStr">
@@ -40292,14 +40292,14 @@
       </c>
       <c r="F1261" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="1262">
       <c r="A1262" t="inlineStr">
         <is>
-          <t>Lakeside Elementary</t>
+          <t>Read Elementary</t>
         </is>
       </c>
       <c r="B1262" t="inlineStr">
@@ -40324,14 +40324,14 @@
       </c>
       <c r="F1262" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="1263">
       <c r="A1263" t="inlineStr">
         <is>
-          <t>Little Chute High</t>
+          <t>Little Chute Middle</t>
         </is>
       </c>
       <c r="B1263" t="inlineStr">
@@ -40356,14 +40356,14 @@
       </c>
       <c r="F1263" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="1264">
       <c r="A1264" t="inlineStr">
         <is>
-          <t>Butte des Morts Elementary</t>
+          <t>Gegan Elementary</t>
         </is>
       </c>
       <c r="B1264" t="inlineStr">
@@ -40388,19 +40388,19 @@
       </c>
       <c r="F1264" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="1265">
       <c r="A1265" t="inlineStr">
         <is>
-          <t>Fox Cities Leadership Academy</t>
+          <t>Tipler Middle</t>
         </is>
       </c>
       <c r="B1265" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1265" t="inlineStr">
@@ -40420,14 +40420,14 @@
       </c>
       <c r="F1265" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
         <is>
-          <t>South Park Middle</t>
+          <t>Wilson Elementary</t>
         </is>
       </c>
       <c r="B1266" t="inlineStr">
@@ -40452,19 +40452,19 @@
       </c>
       <c r="F1266" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="1267">
       <c r="A1267" t="inlineStr">
         <is>
-          <t>Kaleidoscope Academy</t>
+          <t>Hoover Elementary</t>
         </is>
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1267" t="inlineStr">
@@ -40484,19 +40484,19 @@
       </c>
       <c r="F1267" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1268">
       <c r="A1268" t="inlineStr">
         <is>
-          <t>Oakwood Elementary</t>
+          <t>Highlands Elementary</t>
         </is>
       </c>
       <c r="B1268" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1268" t="inlineStr">
@@ -40516,19 +40516,19 @@
       </c>
       <c r="F1268" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1269">
       <c r="A1269" t="inlineStr">
         <is>
-          <t>Chilton High</t>
+          <t>Ready 4 Learning School</t>
         </is>
       </c>
       <c r="B1269" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1269" t="inlineStr">
@@ -40548,14 +40548,14 @@
       </c>
       <c r="F1269" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1270">
       <c r="A1270" t="inlineStr">
         <is>
-          <t>Houdini Elementary</t>
+          <t>Freedom Elementary</t>
         </is>
       </c>
       <c r="B1270" t="inlineStr">
@@ -40580,14 +40580,14 @@
       </c>
       <c r="F1270" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
-          <t>Oaklawn Elementary</t>
+          <t>Coolidge Elementary</t>
         </is>
       </c>
       <c r="B1271" t="inlineStr">
@@ -40612,14 +40612,14 @@
       </c>
       <c r="F1271" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1272">
       <c r="A1272" t="inlineStr">
         <is>
-          <t>Neenah High</t>
+          <t>Roosevelt Elementary</t>
         </is>
       </c>
       <c r="B1272" t="inlineStr">
@@ -40644,19 +40644,19 @@
       </c>
       <c r="F1272" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1273">
       <c r="A1273" t="inlineStr">
         <is>
-          <t>Chilton Elementary</t>
+          <t>North High</t>
         </is>
       </c>
       <c r="B1273" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1273" t="inlineStr">
@@ -40676,14 +40676,14 @@
       </c>
       <c r="F1273" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>213</t>
         </is>
       </c>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
         <is>
-          <t>Lakeview Elementary</t>
+          <t>Roosevelt Elementary</t>
         </is>
       </c>
       <c r="B1274" t="inlineStr">
@@ -40708,14 +40708,14 @@
       </c>
       <c r="F1274" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="1275">
       <c r="A1275" t="inlineStr">
         <is>
-          <t>Horizons Elementary</t>
+          <t>Huntley Elementary</t>
         </is>
       </c>
       <c r="B1275" t="inlineStr">
@@ -40740,7 +40740,7 @@
       </c>
       <c r="F1275" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -40779,12 +40779,12 @@
     <row r="1277">
       <c r="A1277" t="inlineStr">
         <is>
-          <t>Chilton Middle</t>
+          <t>Freedom High</t>
         </is>
       </c>
       <c r="B1277" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1277" t="inlineStr">
@@ -40811,7 +40811,7 @@
     <row r="1278">
       <c r="A1278" t="inlineStr">
         <is>
-          <t>Read Elementary</t>
+          <t>Clayton Elementary</t>
         </is>
       </c>
       <c r="B1278" t="inlineStr">
@@ -40836,19 +40836,19 @@
       </c>
       <c r="F1278" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1279">
       <c r="A1279" t="inlineStr">
         <is>
-          <t>Hoover Elementary</t>
+          <t>Franklin Elementary</t>
         </is>
       </c>
       <c r="B1279" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1279" t="inlineStr">
@@ -40868,19 +40868,19 @@
       </c>
       <c r="F1279" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="1280">
       <c r="A1280" t="inlineStr">
         <is>
-          <t>Highlands Elementary</t>
+          <t>Hilbert Middle</t>
         </is>
       </c>
       <c r="B1280" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1280" t="inlineStr">
@@ -40900,14 +40900,14 @@
       </c>
       <c r="F1280" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
-          <t>Ready 4 Learning School</t>
+          <t>Menasha High</t>
         </is>
       </c>
       <c r="B1281" t="inlineStr">
@@ -40932,14 +40932,14 @@
       </c>
       <c r="F1281" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>61</t>
         </is>
       </c>
     </row>
     <row r="1282">
       <c r="A1282" t="inlineStr">
         <is>
-          <t>Spring Road Elementary</t>
+          <t>Shattuck Middle</t>
         </is>
       </c>
       <c r="B1282" t="inlineStr">
@@ -40964,19 +40964,19 @@
       </c>
       <c r="F1282" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>98</t>
         </is>
       </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
         <is>
-          <t>Freedom Elementary</t>
+          <t>Shapiro STEM Academy</t>
         </is>
       </c>
       <c r="B1283" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1283" t="inlineStr">
@@ -40996,19 +40996,19 @@
       </c>
       <c r="F1283" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="1284">
       <c r="A1284" t="inlineStr">
         <is>
-          <t>Coolidge Elementary</t>
+          <t>Horizons Elementary</t>
         </is>
       </c>
       <c r="B1284" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1284" t="inlineStr">
@@ -41028,19 +41028,19 @@
       </c>
       <c r="F1284" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1285">
       <c r="A1285" t="inlineStr">
         <is>
-          <t>North High</t>
+          <t>Brillion High</t>
         </is>
       </c>
       <c r="B1285" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1285" t="inlineStr">
@@ -41060,19 +41060,19 @@
       </c>
       <c r="F1285" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="1286">
       <c r="A1286" t="inlineStr">
         <is>
-          <t>Huntley Elementary</t>
+          <t>Maplewood Middle</t>
         </is>
       </c>
       <c r="B1286" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1286" t="inlineStr">
@@ -41092,14 +41092,14 @@
       </c>
       <c r="F1286" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>99</t>
         </is>
       </c>
     </row>
     <row r="1287">
       <c r="A1287" t="inlineStr">
         <is>
-          <t>Roosevelt Elementary</t>
+          <t>South Park Middle</t>
         </is>
       </c>
       <c r="B1287" t="inlineStr">
@@ -41124,19 +41124,19 @@
       </c>
       <c r="F1287" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="1288">
       <c r="A1288" t="inlineStr">
         <is>
-          <t>Freedom High</t>
+          <t>Merrill Middle</t>
         </is>
       </c>
       <c r="B1288" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1288" t="inlineStr">
@@ -41156,19 +41156,19 @@
       </c>
       <c r="F1288" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="1289">
       <c r="A1289" t="inlineStr">
         <is>
-          <t>Clayton Elementary</t>
+          <t>Fox Cities Leadership Academy</t>
         </is>
       </c>
       <c r="B1289" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1289" t="inlineStr">
@@ -41188,19 +41188,19 @@
       </c>
       <c r="F1289" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1290">
       <c r="A1290" t="inlineStr">
         <is>
-          <t>Franklin Elementary</t>
+          <t>Spring Road Elementary</t>
         </is>
       </c>
       <c r="B1290" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1290" t="inlineStr">
@@ -41220,14 +41220,14 @@
       </c>
       <c r="F1290" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
-          <t>Brillion Middle</t>
+          <t>Hilbert High</t>
         </is>
       </c>
       <c r="B1291" t="inlineStr">
@@ -41259,12 +41259,12 @@
     <row r="1292">
       <c r="A1292" t="inlineStr">
         <is>
-          <t>Shattuck Middle</t>
+          <t>Chilton Elementary</t>
         </is>
       </c>
       <c r="B1292" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1292" t="inlineStr">
@@ -41284,14 +41284,14 @@
       </c>
       <c r="F1292" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1293">
       <c r="A1293" t="inlineStr">
         <is>
-          <t>Menasha High</t>
+          <t>Jefferson Elementary</t>
         </is>
       </c>
       <c r="B1293" t="inlineStr">
@@ -41316,19 +41316,19 @@
       </c>
       <c r="F1293" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="1294">
       <c r="A1294" t="inlineStr">
         <is>
-          <t>Shapiro STEM Academy</t>
+          <t>Ferber Elementary</t>
         </is>
       </c>
       <c r="B1294" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1294" t="inlineStr">
@@ -41348,14 +41348,14 @@
       </c>
       <c r="F1294" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="1295">
       <c r="A1295" t="inlineStr">
         <is>
-          <t>Brillion High</t>
+          <t>Brillion Middle</t>
         </is>
       </c>
       <c r="B1295" t="inlineStr">
@@ -41380,14 +41380,14 @@
       </c>
       <c r="F1295" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1296">
       <c r="A1296" t="inlineStr">
         <is>
-          <t>Maplewood Middle</t>
+          <t>Oaklawn Elementary</t>
         </is>
       </c>
       <c r="B1296" t="inlineStr">
@@ -41412,19 +41412,19 @@
       </c>
       <c r="F1296" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1297">
       <c r="A1297" t="inlineStr">
         <is>
-          <t>Merrill Middle</t>
+          <t>Chilton Middle</t>
         </is>
       </c>
       <c r="B1297" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1297" t="inlineStr">
@@ -41444,19 +41444,19 @@
       </c>
       <c r="F1297" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
         <is>
-          <t>Roosevelt Elementary</t>
+          <t>Little Chute Elementary</t>
         </is>
       </c>
       <c r="B1298" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1298" t="inlineStr">
@@ -41476,19 +41476,19 @@
       </c>
       <c r="F1298" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="1299">
       <c r="A1299" t="inlineStr">
         <is>
-          <t>Wilson Elementary</t>
+          <t>Seymour Middle</t>
         </is>
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1299" t="inlineStr">
@@ -41508,19 +41508,19 @@
       </c>
       <c r="F1299" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="1300">
       <c r="A1300" t="inlineStr">
         <is>
-          <t>Webster Stanley Middle</t>
+          <t>Ronald C Dunlap Elementary School</t>
         </is>
       </c>
       <c r="B1300" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1300" t="inlineStr">
@@ -41540,14 +41540,14 @@
       </c>
       <c r="F1300" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
-          <t>Seymour Middle</t>
+          <t>Hortonville High</t>
         </is>
       </c>
       <c r="B1301" t="inlineStr">
@@ -41572,19 +41572,19 @@
       </c>
       <c r="F1301" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="1302">
       <c r="A1302" t="inlineStr">
         <is>
-          <t>Patch Elementary</t>
+          <t>Janssen Elementary</t>
         </is>
       </c>
       <c r="B1302" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1302" t="inlineStr">
@@ -41604,19 +41604,19 @@
       </c>
       <c r="F1302" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="1303">
       <c r="A1303" t="inlineStr">
         <is>
-          <t>Franklin Elementary</t>
+          <t>New Holstein Middle</t>
         </is>
       </c>
       <c r="B1303" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1303" t="inlineStr">
@@ -41636,19 +41636,19 @@
       </c>
       <c r="F1303" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="1304">
       <c r="A1304" t="inlineStr">
         <is>
-          <t>New Holstein High</t>
+          <t>Shiocton Elementary</t>
         </is>
       </c>
       <c r="B1304" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1304" t="inlineStr">
@@ -41668,19 +41668,19 @@
       </c>
       <c r="F1304" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="1305">
       <c r="A1305" t="inlineStr">
         <is>
-          <t>Mapleview Intermediate</t>
+          <t>E Cook Elementary</t>
         </is>
       </c>
       <c r="B1305" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1305" t="inlineStr">
@@ -41700,19 +41700,19 @@
       </c>
       <c r="F1305" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1306">
       <c r="A1306" t="inlineStr">
         <is>
-          <t>McKinley Elementary</t>
+          <t>Chilton High</t>
         </is>
       </c>
       <c r="B1306" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1306" t="inlineStr">
@@ -41732,14 +41732,14 @@
       </c>
       <c r="F1306" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="1307">
       <c r="A1307" t="inlineStr">
         <is>
-          <t>Seymour High</t>
+          <t>Gerritts Middle</t>
         </is>
       </c>
       <c r="B1307" t="inlineStr">
@@ -41764,14 +41764,14 @@
       </c>
       <c r="F1307" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="1308">
       <c r="A1308" t="inlineStr">
         <is>
-          <t>Dr H B Tanner Elementary</t>
+          <t>Appleton Technical Academy</t>
         </is>
       </c>
       <c r="B1308" t="inlineStr">
@@ -41803,12 +41803,12 @@
     <row r="1309">
       <c r="A1309" t="inlineStr">
         <is>
-          <t>Kimberly High</t>
+          <t>Oakwood Elementary</t>
         </is>
       </c>
       <c r="B1309" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1309" t="inlineStr">
@@ -41828,14 +41828,14 @@
       </c>
       <c r="F1309" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="1310">
       <c r="A1310" t="inlineStr">
         <is>
-          <t>Badger Elementary</t>
+          <t>Shiocton High</t>
         </is>
       </c>
       <c r="B1310" t="inlineStr">
@@ -41860,14 +41860,14 @@
       </c>
       <c r="F1310" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
-          <t>Richmond Elementary</t>
+          <t>Kaukauna High</t>
         </is>
       </c>
       <c r="B1311" t="inlineStr">
@@ -41892,19 +41892,19 @@
       </c>
       <c r="F1311" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="1312">
       <c r="A1312" t="inlineStr">
         <is>
-          <t>Omro Elementary</t>
+          <t>River View School</t>
         </is>
       </c>
       <c r="B1312" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1312" t="inlineStr">
@@ -41924,14 +41924,14 @@
       </c>
       <c r="F1312" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>105</t>
         </is>
       </c>
     </row>
     <row r="1313">
       <c r="A1313" t="inlineStr">
         <is>
-          <t>Ronald C Dunlap Elementary School</t>
+          <t>North High</t>
         </is>
       </c>
       <c r="B1313" t="inlineStr">
@@ -41956,14 +41956,14 @@
       </c>
       <c r="F1313" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="1314">
       <c r="A1314" t="inlineStr">
         <is>
-          <t>River View School</t>
+          <t>Quinney Elementary</t>
         </is>
       </c>
       <c r="B1314" t="inlineStr">
@@ -41988,19 +41988,19 @@
       </c>
       <c r="F1314" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
         <is>
-          <t>North High</t>
+          <t>Omro Elementary</t>
         </is>
       </c>
       <c r="B1315" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1315" t="inlineStr">
@@ -42020,14 +42020,14 @@
       </c>
       <c r="F1315" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="1316">
       <c r="A1316" t="inlineStr">
         <is>
-          <t>Kaukauna High</t>
+          <t>Richmond Elementary</t>
         </is>
       </c>
       <c r="B1316" t="inlineStr">
@@ -42052,19 +42052,19 @@
       </c>
       <c r="F1316" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1317">
       <c r="A1317" t="inlineStr">
         <is>
-          <t>Haen Elementary</t>
+          <t>Patch Elementary</t>
         </is>
       </c>
       <c r="B1317" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1317" t="inlineStr">
@@ -42084,19 +42084,19 @@
       </c>
       <c r="F1317" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="1318">
       <c r="A1318" t="inlineStr">
         <is>
-          <t>Shiocton High</t>
+          <t>Winneconne High</t>
         </is>
       </c>
       <c r="B1318" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1318" t="inlineStr">
@@ -42116,19 +42116,19 @@
       </c>
       <c r="F1318" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1319">
       <c r="A1319" t="inlineStr">
         <is>
-          <t>New Holstein Middle</t>
+          <t>New Directions Learning Community</t>
         </is>
       </c>
       <c r="B1319" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1319" t="inlineStr">
@@ -42148,14 +42148,14 @@
       </c>
       <c r="F1319" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
         <is>
-          <t>Janssen Elementary</t>
+          <t>Park Community Charter School</t>
         </is>
       </c>
       <c r="B1320" t="inlineStr">
@@ -42180,14 +42180,14 @@
       </c>
       <c r="F1320" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
-          <t>Shiocton Elementary</t>
+          <t>Winneconne Middle</t>
         </is>
       </c>
       <c r="B1321" t="inlineStr">
@@ -42202,7 +42202,7 @@
       </c>
       <c r="D1321" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Amer Indian</t>
         </is>
       </c>
       <c r="E1321" t="inlineStr">
@@ -42212,19 +42212,19 @@
       </c>
       <c r="F1321" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="1322">
       <c r="A1322" t="inlineStr">
         <is>
-          <t>E Cook Elementary</t>
+          <t>Odyssey-Magellan</t>
         </is>
       </c>
       <c r="B1322" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1322" t="inlineStr">
@@ -42244,19 +42244,19 @@
       </c>
       <c r="F1322" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1323">
       <c r="A1323" t="inlineStr">
         <is>
-          <t>Appleton Technical Academy</t>
+          <t>Omro High</t>
         </is>
       </c>
       <c r="B1323" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1323" t="inlineStr">
@@ -42276,14 +42276,14 @@
       </c>
       <c r="F1323" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="1324">
       <c r="A1324" t="inlineStr">
         <is>
-          <t>North Greenville Elementary</t>
+          <t>Renaissance School</t>
         </is>
       </c>
       <c r="B1324" t="inlineStr">
@@ -42308,19 +42308,19 @@
       </c>
       <c r="F1324" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1325">
       <c r="A1325" t="inlineStr">
         <is>
-          <t>Quinney Elementary</t>
+          <t>Omro Middle</t>
         </is>
       </c>
       <c r="B1325" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1325" t="inlineStr">
@@ -42340,19 +42340,19 @@
       </c>
       <c r="F1325" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="1326">
       <c r="A1326" t="inlineStr">
         <is>
-          <t>Westside Elementary</t>
+          <t>Lakeview Elementary</t>
         </is>
       </c>
       <c r="B1326" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1326" t="inlineStr">
@@ -42372,19 +42372,19 @@
       </c>
       <c r="F1326" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1327">
       <c r="A1327" t="inlineStr">
         <is>
-          <t>Omro Middle</t>
+          <t>Badger Elementary</t>
         </is>
       </c>
       <c r="B1327" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1327" t="inlineStr">
@@ -42404,14 +42404,14 @@
       </c>
       <c r="F1327" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="1328">
       <c r="A1328" t="inlineStr">
         <is>
-          <t>Renaissance School</t>
+          <t>Haen Elementary</t>
         </is>
       </c>
       <c r="B1328" t="inlineStr">
@@ -42436,19 +42436,19 @@
       </c>
       <c r="F1328" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="1329">
       <c r="A1329" t="inlineStr">
         <is>
-          <t>Omro High</t>
+          <t>Dr H B Tanner Elementary</t>
         </is>
       </c>
       <c r="B1329" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1329" t="inlineStr">
@@ -42468,19 +42468,19 @@
       </c>
       <c r="F1329" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1330">
       <c r="A1330" t="inlineStr">
         <is>
-          <t>Winneconne Middle</t>
+          <t>Jefferson Elementary</t>
         </is>
       </c>
       <c r="B1330" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1330" t="inlineStr">
@@ -42490,7 +42490,7 @@
       </c>
       <c r="D1330" t="inlineStr">
         <is>
-          <t>Amer Indian</t>
+          <t>White</t>
         </is>
       </c>
       <c r="E1330" t="inlineStr">
@@ -42500,19 +42500,19 @@
       </c>
       <c r="F1330" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
-          <t>Odyssey-Magellan</t>
+          <t>New Holstein Elementary</t>
         </is>
       </c>
       <c r="B1331" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1331" t="inlineStr">
@@ -42532,14 +42532,14 @@
       </c>
       <c r="F1331" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1332">
       <c r="A1332" t="inlineStr">
         <is>
-          <t>Park Community Charter School</t>
+          <t>Columbus Elementary</t>
         </is>
       </c>
       <c r="B1332" t="inlineStr">
@@ -42564,19 +42564,19 @@
       </c>
       <c r="F1332" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1333">
       <c r="A1333" t="inlineStr">
         <is>
-          <t>New Directions Learning Community</t>
+          <t>West High</t>
         </is>
       </c>
       <c r="B1333" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1333" t="inlineStr">
@@ -42596,14 +42596,14 @@
       </c>
       <c r="F1333" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>102</t>
         </is>
       </c>
     </row>
     <row r="1334">
       <c r="A1334" t="inlineStr">
         <is>
-          <t>Hortonville High</t>
+          <t>Little Chute Career Pathways Academy</t>
         </is>
       </c>
       <c r="B1334" t="inlineStr">
@@ -42628,14 +42628,14 @@
       </c>
       <c r="F1334" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1335">
       <c r="A1335" t="inlineStr">
         <is>
-          <t>Rock Ledge Elementary</t>
+          <t>Hortonville Middle</t>
         </is>
       </c>
       <c r="B1335" t="inlineStr">
@@ -42660,19 +42660,19 @@
       </c>
       <c r="F1335" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="1336">
       <c r="A1336" t="inlineStr">
         <is>
-          <t>New Holstein Elementary</t>
+          <t>Woodland Intermediate</t>
         </is>
       </c>
       <c r="B1336" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1336" t="inlineStr">
@@ -42692,14 +42692,14 @@
       </c>
       <c r="F1336" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1337">
       <c r="A1337" t="inlineStr">
         <is>
-          <t>Little Chute Elementary</t>
+          <t>Berry Elementary</t>
         </is>
       </c>
       <c r="B1337" t="inlineStr">
@@ -42724,19 +42724,19 @@
       </c>
       <c r="F1337" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1338">
       <c r="A1338" t="inlineStr">
         <is>
-          <t>Jefferson Elementary</t>
+          <t>Kimberly High</t>
         </is>
       </c>
       <c r="B1338" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1338" t="inlineStr">
@@ -42756,14 +42756,14 @@
       </c>
       <c r="F1338" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="1339">
       <c r="A1339" t="inlineStr">
         <is>
-          <t>Columbus Elementary</t>
+          <t>Tesla Engineering Charter School</t>
         </is>
       </c>
       <c r="B1339" t="inlineStr">
@@ -42788,19 +42788,19 @@
       </c>
       <c r="F1339" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1340">
       <c r="A1340" t="inlineStr">
         <is>
-          <t>West High</t>
+          <t>Madison Middle</t>
         </is>
       </c>
       <c r="B1340" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1340" t="inlineStr">
@@ -42820,14 +42820,14 @@
       </c>
       <c r="F1340" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
-          <t>Little Chute Career Pathways Academy</t>
+          <t>Rock Ledge Elementary</t>
         </is>
       </c>
       <c r="B1341" t="inlineStr">
@@ -42852,14 +42852,14 @@
       </c>
       <c r="F1341" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="1342">
       <c r="A1342" t="inlineStr">
         <is>
-          <t>Hortonville Middle</t>
+          <t>Westside Elementary</t>
         </is>
       </c>
       <c r="B1342" t="inlineStr">
@@ -42884,14 +42884,14 @@
       </c>
       <c r="F1342" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="1343">
       <c r="A1343" t="inlineStr">
         <is>
-          <t>Woodland Intermediate</t>
+          <t>McKinley Elementary</t>
         </is>
       </c>
       <c r="B1343" t="inlineStr">
@@ -42923,7 +42923,7 @@
     <row r="1344">
       <c r="A1344" t="inlineStr">
         <is>
-          <t>Berry Elementary</t>
+          <t>Seymour High</t>
         </is>
       </c>
       <c r="B1344" t="inlineStr">
@@ -42948,19 +42948,19 @@
       </c>
       <c r="F1344" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="1345">
       <c r="A1345" t="inlineStr">
         <is>
-          <t>Tesla Engineering Charter School</t>
+          <t>New Holstein High</t>
         </is>
       </c>
       <c r="B1345" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1345" t="inlineStr">
@@ -42980,14 +42980,14 @@
       </c>
       <c r="F1345" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="1346">
       <c r="A1346" t="inlineStr">
         <is>
-          <t>Madison Middle</t>
+          <t>Houdini Elementary</t>
         </is>
       </c>
       <c r="B1346" t="inlineStr">
@@ -43012,19 +43012,19 @@
       </c>
       <c r="F1346" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="1347">
       <c r="A1347" t="inlineStr">
         <is>
-          <t>Winneconne High</t>
+          <t>Mapleview Intermediate</t>
         </is>
       </c>
       <c r="B1347" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1347" t="inlineStr">
@@ -43044,19 +43044,19 @@
       </c>
       <c r="F1347" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
         <is>
-          <t>Gerritts Middle</t>
+          <t>Franklin Elementary</t>
         </is>
       </c>
       <c r="B1348" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1348" t="inlineStr">
@@ -43076,46 +43076,46 @@
       </c>
       <c r="F1348" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="1349">
       <c r="A1349" t="inlineStr">
         <is>
-          <t>Omro High</t>
+          <t>North Greenville Elementary</t>
         </is>
       </c>
       <c r="B1349" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1349" t="inlineStr">
         <is>
-          <t>Grade Level</t>
+          <t>Race/Ethnicity</t>
         </is>
       </c>
       <c r="D1349" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>White</t>
         </is>
       </c>
       <c r="E1349" t="inlineStr">
         <is>
-          <t>X1012</t>
+          <t>W</t>
         </is>
       </c>
       <c r="F1349" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1350">
       <c r="A1350" t="inlineStr">
         <is>
-          <t>Chilton High</t>
+          <t>New Holstein High</t>
         </is>
       </c>
       <c r="B1350" t="inlineStr">
@@ -43140,14 +43140,14 @@
       </c>
       <c r="F1350" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
-          <t>Freedom High</t>
+          <t>West High</t>
         </is>
       </c>
       <c r="B1351" t="inlineStr">
@@ -43172,14 +43172,14 @@
       </c>
       <c r="F1351" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="1352">
       <c r="A1352" t="inlineStr">
         <is>
-          <t>Shiocton High</t>
+          <t>Little Chute High</t>
         </is>
       </c>
       <c r="B1352" t="inlineStr">
@@ -43204,19 +43204,19 @@
       </c>
       <c r="F1352" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="1353">
       <c r="A1353" t="inlineStr">
         <is>
-          <t>Winneconne High</t>
+          <t>Chilton High</t>
         </is>
       </c>
       <c r="B1353" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1353" t="inlineStr">
@@ -43236,14 +43236,14 @@
       </c>
       <c r="F1353" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1354">
       <c r="A1354" t="inlineStr">
         <is>
-          <t>Appleton Technical Academy</t>
+          <t>Freedom High</t>
         </is>
       </c>
       <c r="B1354" t="inlineStr">
@@ -43268,14 +43268,14 @@
       </c>
       <c r="F1354" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1355">
       <c r="A1355" t="inlineStr">
         <is>
-          <t>Little Chute High</t>
+          <t>East High</t>
         </is>
       </c>
       <c r="B1355" t="inlineStr">
@@ -43300,14 +43300,14 @@
       </c>
       <c r="F1355" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="1356">
       <c r="A1356" t="inlineStr">
         <is>
-          <t>West High</t>
+          <t>Valley New School</t>
         </is>
       </c>
       <c r="B1356" t="inlineStr">
@@ -43332,19 +43332,19 @@
       </c>
       <c r="F1356" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1357">
       <c r="A1357" t="inlineStr">
         <is>
-          <t>Valley New School</t>
+          <t>Winneconne High</t>
         </is>
       </c>
       <c r="B1357" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1357" t="inlineStr">
@@ -43371,12 +43371,12 @@
     <row r="1358">
       <c r="A1358" t="inlineStr">
         <is>
-          <t>New Holstein High</t>
+          <t>Neenah High</t>
         </is>
       </c>
       <c r="B1358" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1358" t="inlineStr">
@@ -43396,14 +43396,14 @@
       </c>
       <c r="F1358" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="1359">
       <c r="A1359" t="inlineStr">
         <is>
-          <t>Seymour High</t>
+          <t>Kimberly High</t>
         </is>
       </c>
       <c r="B1359" t="inlineStr">
@@ -43428,7 +43428,7 @@
       </c>
       <c r="F1359" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -43467,12 +43467,12 @@
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
-          <t>Brillion High</t>
+          <t>Hortonville High</t>
         </is>
       </c>
       <c r="B1361" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1361" t="inlineStr">
@@ -43492,19 +43492,19 @@
       </c>
       <c r="F1361" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="1362">
       <c r="A1362" t="inlineStr">
         <is>
-          <t>Hortonville High</t>
+          <t>Brillion High</t>
         </is>
       </c>
       <c r="B1362" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1362" t="inlineStr">
@@ -43524,14 +43524,14 @@
       </c>
       <c r="F1362" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1363">
       <c r="A1363" t="inlineStr">
         <is>
-          <t>Kimberly High</t>
+          <t>North High</t>
         </is>
       </c>
       <c r="B1363" t="inlineStr">
@@ -43556,14 +43556,14 @@
       </c>
       <c r="F1363" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="1364">
       <c r="A1364" t="inlineStr">
         <is>
-          <t>Neenah High</t>
+          <t>Menasha High</t>
         </is>
       </c>
       <c r="B1364" t="inlineStr">
@@ -43588,14 +43588,14 @@
       </c>
       <c r="F1364" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>51</t>
         </is>
       </c>
     </row>
     <row r="1365">
       <c r="A1365" t="inlineStr">
         <is>
-          <t>North High</t>
+          <t>Seymour High</t>
         </is>
       </c>
       <c r="B1365" t="inlineStr">
@@ -43620,19 +43620,19 @@
       </c>
       <c r="F1365" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="1366">
       <c r="A1366" t="inlineStr">
         <is>
-          <t>Menasha High</t>
+          <t>Shiocton High</t>
         </is>
       </c>
       <c r="B1366" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1366" t="inlineStr">
@@ -43652,14 +43652,14 @@
       </c>
       <c r="F1366" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1367">
       <c r="A1367" t="inlineStr">
         <is>
-          <t>East High</t>
+          <t>Appleton Technical Academy</t>
         </is>
       </c>
       <c r="B1367" t="inlineStr">
@@ -43684,19 +43684,19 @@
       </c>
       <c r="F1367" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>West High</t>
+          <t>Kaukauna High</t>
         </is>
       </c>
       <c r="B1368" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1368" t="inlineStr">
@@ -43716,19 +43716,19 @@
       </c>
       <c r="F1368" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="1369">
       <c r="A1369" t="inlineStr">
         <is>
-          <t>Kaukauna High</t>
+          <t>Hilbert High</t>
         </is>
       </c>
       <c r="B1369" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1369" t="inlineStr">
@@ -43748,19 +43748,19 @@
       </c>
       <c r="F1369" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1370">
       <c r="A1370" t="inlineStr">
         <is>
-          <t>Hilbert High</t>
+          <t>Omro High</t>
         </is>
       </c>
       <c r="B1370" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1370" t="inlineStr">
@@ -43780,7 +43780,7 @@
       </c>
       <c r="F1370" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -43802,17 +43802,17 @@
       </c>
       <c r="D1371" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E1371" t="inlineStr">
         <is>
-          <t>X113</t>
+          <t>X1012</t>
         </is>
       </c>
       <c r="F1371" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -43851,12 +43851,12 @@
     <row r="1373">
       <c r="A1373" t="inlineStr">
         <is>
-          <t>Little Chute High</t>
+          <t>Menasha High</t>
         </is>
       </c>
       <c r="B1373" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1373" t="inlineStr">
@@ -43876,14 +43876,14 @@
       </c>
       <c r="F1373" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="1374">
       <c r="A1374" t="inlineStr">
         <is>
-          <t>Kaukauna High</t>
+          <t>Fox Cities Leadership Academy</t>
         </is>
       </c>
       <c r="B1374" t="inlineStr">
@@ -43908,14 +43908,14 @@
       </c>
       <c r="F1374" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1375">
       <c r="A1375" t="inlineStr">
         <is>
-          <t>Seymour High</t>
+          <t>Hortonville High</t>
         </is>
       </c>
       <c r="B1375" t="inlineStr">
@@ -43940,14 +43940,14 @@
       </c>
       <c r="F1375" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="1376">
       <c r="A1376" t="inlineStr">
         <is>
-          <t>Kimberly High</t>
+          <t>Little Chute High</t>
         </is>
       </c>
       <c r="B1376" t="inlineStr">
@@ -43972,19 +43972,19 @@
       </c>
       <c r="F1376" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1377">
       <c r="A1377" t="inlineStr">
         <is>
-          <t>Fox Cities Leadership Academy</t>
+          <t>West High</t>
         </is>
       </c>
       <c r="B1377" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1377" t="inlineStr">
@@ -44004,14 +44004,14 @@
       </c>
       <c r="F1377" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="1378">
       <c r="A1378" t="inlineStr">
         <is>
-          <t>Shiocton High</t>
+          <t>Seymour High</t>
         </is>
       </c>
       <c r="B1378" t="inlineStr">
@@ -44036,19 +44036,19 @@
       </c>
       <c r="F1378" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="1379">
       <c r="A1379" t="inlineStr">
         <is>
-          <t>Menasha High</t>
+          <t>Kimberly High</t>
         </is>
       </c>
       <c r="B1379" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1379" t="inlineStr">
@@ -44068,14 +44068,14 @@
       </c>
       <c r="F1379" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="1380">
       <c r="A1380" t="inlineStr">
         <is>
-          <t>Freedom High</t>
+          <t>Kaukauna High</t>
         </is>
       </c>
       <c r="B1380" t="inlineStr">
@@ -44100,14 +44100,14 @@
       </c>
       <c r="F1380" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
-          <t>Hortonville High</t>
+          <t>Shiocton High</t>
         </is>
       </c>
       <c r="B1381" t="inlineStr">
@@ -44132,19 +44132,19 @@
       </c>
       <c r="F1381" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1382">
       <c r="A1382" t="inlineStr">
         <is>
-          <t>Neenah High</t>
+          <t>Freedom High</t>
         </is>
       </c>
       <c r="B1382" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1382" t="inlineStr">
@@ -44164,19 +44164,19 @@
       </c>
       <c r="F1382" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="1383">
       <c r="A1383" t="inlineStr">
         <is>
-          <t>Renaissance School</t>
+          <t>Neenah High</t>
         </is>
       </c>
       <c r="B1383" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1383" t="inlineStr">
@@ -44196,14 +44196,14 @@
       </c>
       <c r="F1383" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="1384">
       <c r="A1384" t="inlineStr">
         <is>
-          <t>North High</t>
+          <t>Renaissance School</t>
         </is>
       </c>
       <c r="B1384" t="inlineStr">
@@ -44228,19 +44228,19 @@
       </c>
       <c r="F1384" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1385">
       <c r="A1385" t="inlineStr">
         <is>
-          <t>North High</t>
+          <t>West High</t>
         </is>
       </c>
       <c r="B1385" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1385" t="inlineStr">
@@ -44260,14 +44260,14 @@
       </c>
       <c r="F1385" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="1386">
       <c r="A1386" t="inlineStr">
         <is>
-          <t>West High</t>
+          <t>Tesla Engineering Charter School</t>
         </is>
       </c>
       <c r="B1386" t="inlineStr">
@@ -44292,14 +44292,14 @@
       </c>
       <c r="F1386" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1387">
       <c r="A1387" t="inlineStr">
         <is>
-          <t>Brillion High</t>
+          <t>New Holstein High</t>
         </is>
       </c>
       <c r="B1387" t="inlineStr">
@@ -44331,12 +44331,12 @@
     <row r="1388">
       <c r="A1388" t="inlineStr">
         <is>
-          <t>Omro High</t>
+          <t>Brillion High</t>
         </is>
       </c>
       <c r="B1388" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1388" t="inlineStr">
@@ -44356,19 +44356,19 @@
       </c>
       <c r="F1388" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1389">
       <c r="A1389" t="inlineStr">
         <is>
-          <t>New Holstein High</t>
+          <t>North High</t>
         </is>
       </c>
       <c r="B1389" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1389" t="inlineStr">
@@ -44388,19 +44388,19 @@
       </c>
       <c r="F1389" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>114</t>
         </is>
       </c>
     </row>
     <row r="1390">
       <c r="A1390" t="inlineStr">
         <is>
-          <t>Tesla Engineering Charter School</t>
+          <t>Omro High</t>
         </is>
       </c>
       <c r="B1390" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1390" t="inlineStr">
@@ -44420,19 +44420,19 @@
       </c>
       <c r="F1390" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
-          <t>Chilton High</t>
+          <t>North High</t>
         </is>
       </c>
       <c r="B1391" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1391" t="inlineStr">
@@ -44452,19 +44452,19 @@
       </c>
       <c r="F1391" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="1392">
       <c r="A1392" t="inlineStr">
         <is>
-          <t>Kimberly High</t>
+          <t>Chilton High</t>
         </is>
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1392" t="inlineStr">
@@ -44474,17 +44474,17 @@
       </c>
       <c r="D1392" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E1392" t="inlineStr">
         <is>
-          <t>X1210</t>
+          <t>X113</t>
         </is>
       </c>
       <c r="F1392" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -44523,7 +44523,7 @@
     <row r="1394">
       <c r="A1394" t="inlineStr">
         <is>
-          <t>Hortonville High</t>
+          <t>Tesla Engineering Charter School</t>
         </is>
       </c>
       <c r="B1394" t="inlineStr">
@@ -44548,19 +44548,19 @@
       </c>
       <c r="F1394" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>West High</t>
+          <t>Shiocton High</t>
         </is>
       </c>
       <c r="B1395" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1395" t="inlineStr">
@@ -44580,14 +44580,14 @@
       </c>
       <c r="F1395" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1396">
       <c r="A1396" t="inlineStr">
         <is>
-          <t>Shiocton High</t>
+          <t>Kaukauna High</t>
         </is>
       </c>
       <c r="B1396" t="inlineStr">
@@ -44612,19 +44612,19 @@
       </c>
       <c r="F1396" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="1397">
       <c r="A1397" t="inlineStr">
         <is>
-          <t>Little Chute High</t>
+          <t>West High</t>
         </is>
       </c>
       <c r="B1397" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1397" t="inlineStr">
@@ -44644,19 +44644,19 @@
       </c>
       <c r="F1397" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="1398">
       <c r="A1398" t="inlineStr">
         <is>
-          <t>Kaukauna High</t>
+          <t>Menasha High</t>
         </is>
       </c>
       <c r="B1398" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1398" t="inlineStr">
@@ -44676,14 +44676,14 @@
       </c>
       <c r="F1398" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>North High</t>
+          <t>Kimberly High</t>
         </is>
       </c>
       <c r="B1399" t="inlineStr">
@@ -44708,19 +44708,19 @@
       </c>
       <c r="F1399" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="1400">
       <c r="A1400" t="inlineStr">
         <is>
-          <t>East High</t>
+          <t>New Holstein High</t>
         </is>
       </c>
       <c r="B1400" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1400" t="inlineStr">
@@ -44740,7 +44740,7 @@
       </c>
       <c r="F1400" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -44752,7 +44752,7 @@
       </c>
       <c r="B1401" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1401" t="inlineStr">
@@ -44772,19 +44772,19 @@
       </c>
       <c r="F1401" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="1402">
       <c r="A1402" t="inlineStr">
         <is>
-          <t>Menasha High</t>
+          <t>Little Chute High</t>
         </is>
       </c>
       <c r="B1402" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1402" t="inlineStr">
@@ -44804,19 +44804,19 @@
       </c>
       <c r="F1402" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="1403">
       <c r="A1403" t="inlineStr">
         <is>
-          <t>West High</t>
+          <t>North High</t>
         </is>
       </c>
       <c r="B1403" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1403" t="inlineStr">
@@ -44836,14 +44836,14 @@
       </c>
       <c r="F1403" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="1404">
       <c r="A1404" t="inlineStr">
         <is>
-          <t>Seymour High</t>
+          <t>Hortonville High</t>
         </is>
       </c>
       <c r="B1404" t="inlineStr">
@@ -44868,19 +44868,19 @@
       </c>
       <c r="F1404" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1405">
       <c r="A1405" t="inlineStr">
         <is>
-          <t>New Holstein High</t>
+          <t>Neenah High</t>
         </is>
       </c>
       <c r="B1405" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1405" t="inlineStr">
@@ -44900,7 +44900,7 @@
       </c>
       <c r="F1405" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -44939,12 +44939,12 @@
     <row r="1407">
       <c r="A1407" t="inlineStr">
         <is>
-          <t>Tesla Engineering Charter School</t>
+          <t>Omro High</t>
         </is>
       </c>
       <c r="B1407" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1407" t="inlineStr">
@@ -44964,19 +44964,19 @@
       </c>
       <c r="F1407" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>Omro High</t>
+          <t>Seymour High</t>
         </is>
       </c>
       <c r="B1408" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1408" t="inlineStr">
@@ -44996,19 +44996,19 @@
       </c>
       <c r="F1408" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1409">
       <c r="A1409" t="inlineStr">
         <is>
-          <t>Neenah High</t>
+          <t>East High</t>
         </is>
       </c>
       <c r="B1409" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1409" t="inlineStr">
@@ -45028,14 +45028,14 @@
       </c>
       <c r="F1409" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="1410">
       <c r="A1410" t="inlineStr">
         <is>
-          <t>Westside Elementary</t>
+          <t>West High</t>
         </is>
       </c>
       <c r="B1410" t="inlineStr">
@@ -45050,29 +45050,29 @@
       </c>
       <c r="D1410" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E1410" t="inlineStr">
         <is>
-          <t>X1S2</t>
+          <t>X1210</t>
         </is>
       </c>
       <c r="F1410" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
-          <t>Little Chute Elementary</t>
+          <t>Merrill Elementary</t>
         </is>
       </c>
       <c r="B1411" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1411" t="inlineStr">
@@ -45092,19 +45092,19 @@
       </c>
       <c r="F1411" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="1412">
       <c r="A1412" t="inlineStr">
         <is>
-          <t>Badger Elementary</t>
+          <t>Gegan Elementary</t>
         </is>
       </c>
       <c r="B1412" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1412" t="inlineStr">
@@ -45124,14 +45124,14 @@
       </c>
       <c r="F1412" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="1413">
       <c r="A1413" t="inlineStr">
         <is>
-          <t>Dr H B Tanner Elementary</t>
+          <t>Westside Elementary</t>
         </is>
       </c>
       <c r="B1413" t="inlineStr">
@@ -45156,19 +45156,19 @@
       </c>
       <c r="F1413" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1414">
       <c r="A1414" t="inlineStr">
         <is>
-          <t>Jefferson Elementary</t>
+          <t>Highlands Elementary</t>
         </is>
       </c>
       <c r="B1414" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1414" t="inlineStr">
@@ -45188,14 +45188,14 @@
       </c>
       <c r="F1414" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="1415">
       <c r="A1415" t="inlineStr">
         <is>
-          <t>Jefferson Elementary</t>
+          <t>Clovis Grove Elementary</t>
         </is>
       </c>
       <c r="B1415" t="inlineStr">
@@ -45220,14 +45220,14 @@
       </c>
       <c r="F1415" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1416">
       <c r="A1416" t="inlineStr">
         <is>
-          <t>Columbus Elementary</t>
+          <t>Greenville Elementary</t>
         </is>
       </c>
       <c r="B1416" t="inlineStr">
@@ -45259,12 +45259,12 @@
     <row r="1417">
       <c r="A1417" t="inlineStr">
         <is>
-          <t>Haen Elementary</t>
+          <t>Washington Elementary</t>
         </is>
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1417" t="inlineStr">
@@ -45284,14 +45284,14 @@
       </c>
       <c r="F1417" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="1418">
       <c r="A1418" t="inlineStr">
         <is>
-          <t>Franklin Elementary</t>
+          <t>Jefferson Elementary</t>
         </is>
       </c>
       <c r="B1418" t="inlineStr">
@@ -45316,19 +45316,19 @@
       </c>
       <c r="F1418" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1419">
       <c r="A1419" t="inlineStr">
         <is>
-          <t>North Greenville Elementary</t>
+          <t>Shapiro STEM Academy</t>
         </is>
       </c>
       <c r="B1419" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1419" t="inlineStr">
@@ -45348,19 +45348,19 @@
       </c>
       <c r="F1419" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1420">
       <c r="A1420" t="inlineStr">
         <is>
-          <t>Shapiro STEM Academy</t>
+          <t>North Greenville Elementary</t>
         </is>
       </c>
       <c r="B1420" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1420" t="inlineStr">
@@ -45380,7 +45380,7 @@
       </c>
       <c r="F1420" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -45419,12 +45419,12 @@
     <row r="1422">
       <c r="A1422" t="inlineStr">
         <is>
-          <t>Highlands Elementary</t>
+          <t>Jefferson Elementary</t>
         </is>
       </c>
       <c r="B1422" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1422" t="inlineStr">
@@ -45444,7 +45444,7 @@
       </c>
       <c r="F1422" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -45483,7 +45483,7 @@
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>Hoover Elementary</t>
+          <t>Butte des Morts Elementary</t>
         </is>
       </c>
       <c r="B1424" t="inlineStr">
@@ -45508,19 +45508,19 @@
       </c>
       <c r="F1424" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1425">
       <c r="A1425" t="inlineStr">
         <is>
-          <t>Greenville Elementary</t>
+          <t>New Holstein Elementary</t>
         </is>
       </c>
       <c r="B1425" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1425" t="inlineStr">
@@ -45540,14 +45540,14 @@
       </c>
       <c r="F1425" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1426">
       <c r="A1426" t="inlineStr">
         <is>
-          <t>Washington Elementary</t>
+          <t>Lakeside Elementary</t>
         </is>
       </c>
       <c r="B1426" t="inlineStr">
@@ -45572,14 +45572,14 @@
       </c>
       <c r="F1426" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1427">
       <c r="A1427" t="inlineStr">
         <is>
-          <t>Clovis Grove Elementary</t>
+          <t>Banta School</t>
         </is>
       </c>
       <c r="B1427" t="inlineStr">
@@ -45604,19 +45604,19 @@
       </c>
       <c r="F1427" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1428">
       <c r="A1428" t="inlineStr">
         <is>
-          <t>New Holstein Elementary</t>
+          <t>Columbus Elementary</t>
         </is>
       </c>
       <c r="B1428" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1428" t="inlineStr">
@@ -45636,19 +45636,19 @@
       </c>
       <c r="F1428" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1429">
       <c r="A1429" t="inlineStr">
         <is>
-          <t>Read Elementary</t>
+          <t>Little Chute Elementary</t>
         </is>
       </c>
       <c r="B1429" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1429" t="inlineStr">
@@ -45668,14 +45668,14 @@
       </c>
       <c r="F1429" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1430">
       <c r="A1430" t="inlineStr">
         <is>
-          <t>Patch Elementary</t>
+          <t>Webster Stanley Elementary</t>
         </is>
       </c>
       <c r="B1430" t="inlineStr">
@@ -45700,7 +45700,7 @@
       </c>
       <c r="F1430" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -45739,7 +45739,7 @@
     <row r="1432">
       <c r="A1432" t="inlineStr">
         <is>
-          <t>Houdini Elementary</t>
+          <t>Dr H B Tanner Elementary</t>
         </is>
       </c>
       <c r="B1432" t="inlineStr">
@@ -45764,19 +45764,19 @@
       </c>
       <c r="F1432" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1433">
       <c r="A1433" t="inlineStr">
         <is>
-          <t>Banta School</t>
+          <t>Freedom Elementary</t>
         </is>
       </c>
       <c r="B1433" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1433" t="inlineStr">
@@ -45796,14 +45796,14 @@
       </c>
       <c r="F1433" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1434">
       <c r="A1434" t="inlineStr">
         <is>
-          <t>Gegan Elementary</t>
+          <t>Read Elementary</t>
         </is>
       </c>
       <c r="B1434" t="inlineStr">
@@ -45828,14 +45828,14 @@
       </c>
       <c r="F1434" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="1435">
       <c r="A1435" t="inlineStr">
         <is>
-          <t>Park Community Charter School</t>
+          <t>Badger Elementary</t>
         </is>
       </c>
       <c r="B1435" t="inlineStr">
@@ -45860,19 +45860,19 @@
       </c>
       <c r="F1435" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1436">
       <c r="A1436" t="inlineStr">
         <is>
-          <t>Freedom Elementary</t>
+          <t>Hoover Elementary</t>
         </is>
       </c>
       <c r="B1436" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1436" t="inlineStr">
@@ -45892,14 +45892,14 @@
       </c>
       <c r="F1436" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1437">
       <c r="A1437" t="inlineStr">
         <is>
-          <t>Lakeside Elementary</t>
+          <t>Franklin Elementary</t>
         </is>
       </c>
       <c r="B1437" t="inlineStr">
@@ -45924,14 +45924,14 @@
       </c>
       <c r="F1437" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1438">
       <c r="A1438" t="inlineStr">
         <is>
-          <t>Merrill Elementary</t>
+          <t>Patch Elementary</t>
         </is>
       </c>
       <c r="B1438" t="inlineStr">
@@ -45956,19 +45956,19 @@
       </c>
       <c r="F1438" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="1439">
       <c r="A1439" t="inlineStr">
         <is>
-          <t>Butte des Morts Elementary</t>
+          <t>Houdini Elementary</t>
         </is>
       </c>
       <c r="B1439" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1439" t="inlineStr">
@@ -45988,7 +45988,7 @@
       </c>
       <c r="F1439" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -46027,12 +46027,12 @@
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
-          <t>Webster Stanley Elementary</t>
+          <t>Park Community Charter School</t>
         </is>
       </c>
       <c r="B1441" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1441" t="inlineStr">
@@ -46059,12 +46059,12 @@
     <row r="1442">
       <c r="A1442" t="inlineStr">
         <is>
-          <t>Butte des Morts Elementary</t>
+          <t>Haen Elementary</t>
         </is>
       </c>
       <c r="B1442" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1442" t="inlineStr">
@@ -46074,29 +46074,29 @@
       </c>
       <c r="D1442" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E1442" t="inlineStr">
         <is>
-          <t>X2N2</t>
+          <t>X1S2</t>
         </is>
       </c>
       <c r="F1442" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="1443">
       <c r="A1443" t="inlineStr">
         <is>
-          <t>Berry Elementary</t>
+          <t>Gegan Elementary</t>
         </is>
       </c>
       <c r="B1443" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1443" t="inlineStr">
@@ -46116,14 +46116,14 @@
       </c>
       <c r="F1443" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="1444">
       <c r="A1444" t="inlineStr">
         <is>
-          <t>Washington Elementary</t>
+          <t>Read Elementary</t>
         </is>
       </c>
       <c r="B1444" t="inlineStr">
@@ -46148,19 +46148,19 @@
       </c>
       <c r="F1444" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="1445">
       <c r="A1445" t="inlineStr">
         <is>
-          <t>Traeger Elementary</t>
+          <t>Park Community Charter School</t>
         </is>
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1445" t="inlineStr">
@@ -46180,19 +46180,19 @@
       </c>
       <c r="F1445" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="1446">
       <c r="A1446" t="inlineStr">
         <is>
-          <t>Rock Ledge Elementary</t>
+          <t>Wilson Elementary</t>
         </is>
       </c>
       <c r="B1446" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1446" t="inlineStr">
@@ -46212,14 +46212,14 @@
       </c>
       <c r="F1446" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1447">
       <c r="A1447" t="inlineStr">
         <is>
-          <t>Wilson Elementary</t>
+          <t>Roosevelt Elementary</t>
         </is>
       </c>
       <c r="B1447" t="inlineStr">
@@ -46251,7 +46251,7 @@
     <row r="1448">
       <c r="A1448" t="inlineStr">
         <is>
-          <t>Jefferson Elementary</t>
+          <t>Traeger Elementary</t>
         </is>
       </c>
       <c r="B1448" t="inlineStr">
@@ -46276,19 +46276,19 @@
       </c>
       <c r="F1448" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1449">
       <c r="A1449" t="inlineStr">
         <is>
-          <t>Gegan Elementary</t>
+          <t>New Directions Learning Community</t>
         </is>
       </c>
       <c r="B1449" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1449" t="inlineStr">
@@ -46308,19 +46308,19 @@
       </c>
       <c r="F1449" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1450">
       <c r="A1450" t="inlineStr">
         <is>
-          <t>Jefferson Elementary</t>
+          <t>Greenville Elementary</t>
         </is>
       </c>
       <c r="B1450" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1450" t="inlineStr">
@@ -46340,19 +46340,19 @@
       </c>
       <c r="F1450" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
-          <t>Ferber Elementary</t>
+          <t>Merrill Elementary</t>
         </is>
       </c>
       <c r="B1451" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1451" t="inlineStr">
@@ -46372,14 +46372,14 @@
       </c>
       <c r="F1451" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="1452">
       <c r="A1452" t="inlineStr">
         <is>
-          <t>Little Chute Elementary</t>
+          <t>Quinney Elementary</t>
         </is>
       </c>
       <c r="B1452" t="inlineStr">
@@ -46404,19 +46404,19 @@
       </c>
       <c r="F1452" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="1453">
       <c r="A1453" t="inlineStr">
         <is>
-          <t>Johnston Elementary</t>
+          <t>Jefferson Elementary</t>
         </is>
       </c>
       <c r="B1453" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1453" t="inlineStr">
@@ -46436,19 +46436,19 @@
       </c>
       <c r="F1453" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="1454">
       <c r="A1454" t="inlineStr">
         <is>
-          <t>Greenville Elementary</t>
+          <t>Butte des Morts Elementary</t>
         </is>
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1454" t="inlineStr">
@@ -46468,14 +46468,14 @@
       </c>
       <c r="F1454" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1455">
       <c r="A1455" t="inlineStr">
         <is>
-          <t>Clovis Grove Elementary</t>
+          <t>Omro Elementary</t>
         </is>
       </c>
       <c r="B1455" t="inlineStr">
@@ -46500,19 +46500,19 @@
       </c>
       <c r="F1455" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1456">
       <c r="A1456" t="inlineStr">
         <is>
-          <t>Edison Elementary</t>
+          <t>Clovis Grove Elementary</t>
         </is>
       </c>
       <c r="B1456" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1456" t="inlineStr">
@@ -46532,14 +46532,14 @@
       </c>
       <c r="F1456" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="1457">
       <c r="A1457" t="inlineStr">
         <is>
-          <t>Merrill Elementary</t>
+          <t>Washington Elementary</t>
         </is>
       </c>
       <c r="B1457" t="inlineStr">
@@ -46564,19 +46564,19 @@
       </c>
       <c r="F1457" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="1458">
       <c r="A1458" t="inlineStr">
         <is>
-          <t>Read Elementary</t>
+          <t>Johnston Elementary</t>
         </is>
       </c>
       <c r="B1458" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1458" t="inlineStr">
@@ -46596,14 +46596,14 @@
       </c>
       <c r="F1458" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1459">
       <c r="A1459" t="inlineStr">
         <is>
-          <t>Westside Elementary</t>
+          <t>Houdini Elementary</t>
         </is>
       </c>
       <c r="B1459" t="inlineStr">
@@ -46628,14 +46628,14 @@
       </c>
       <c r="F1459" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1460">
       <c r="A1460" t="inlineStr">
         <is>
-          <t>New Directions Learning Community</t>
+          <t>Edison Elementary</t>
         </is>
       </c>
       <c r="B1460" t="inlineStr">
@@ -46660,14 +46660,14 @@
       </c>
       <c r="F1460" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
-          <t>Park Community Charter School</t>
+          <t>Ferber Elementary</t>
         </is>
       </c>
       <c r="B1461" t="inlineStr">
@@ -46692,7 +46692,7 @@
       </c>
       <c r="F1461" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -46704,7 +46704,7 @@
       </c>
       <c r="B1462" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1462" t="inlineStr">
@@ -46724,19 +46724,19 @@
       </c>
       <c r="F1462" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="1463">
       <c r="A1463" t="inlineStr">
         <is>
-          <t>Franklin Elementary</t>
+          <t>E Cook Elementary</t>
         </is>
       </c>
       <c r="B1463" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1463" t="inlineStr">
@@ -46763,7 +46763,7 @@
     <row r="1464">
       <c r="A1464" t="inlineStr">
         <is>
-          <t>Houdini Elementary</t>
+          <t>Haen Elementary</t>
         </is>
       </c>
       <c r="B1464" t="inlineStr">
@@ -46788,14 +46788,14 @@
       </c>
       <c r="F1464" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="1465">
       <c r="A1465" t="inlineStr">
         <is>
-          <t>Quinney Elementary</t>
+          <t>Jefferson Elementary</t>
         </is>
       </c>
       <c r="B1465" t="inlineStr">
@@ -46820,19 +46820,19 @@
       </c>
       <c r="F1465" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1466">
       <c r="A1466" t="inlineStr">
         <is>
-          <t>Roosevelt Elementary</t>
+          <t>Rock Ledge Elementary</t>
         </is>
       </c>
       <c r="B1466" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1466" t="inlineStr">
@@ -46852,7 +46852,7 @@
       </c>
       <c r="F1466" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -46891,12 +46891,12 @@
     <row r="1468">
       <c r="A1468" t="inlineStr">
         <is>
-          <t>E Cook Elementary</t>
+          <t>Berry Elementary</t>
         </is>
       </c>
       <c r="B1468" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1468" t="inlineStr">
@@ -46923,12 +46923,12 @@
     <row r="1469">
       <c r="A1469" t="inlineStr">
         <is>
-          <t>Shiocton Elementary</t>
+          <t>Coolidge Elementary</t>
         </is>
       </c>
       <c r="B1469" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1469" t="inlineStr">
@@ -46948,19 +46948,19 @@
       </c>
       <c r="F1469" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1470">
       <c r="A1470" t="inlineStr">
         <is>
-          <t>Coolidge Elementary</t>
+          <t>Shiocton Elementary</t>
         </is>
       </c>
       <c r="B1470" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1470" t="inlineStr">
@@ -46980,14 +46980,14 @@
       </c>
       <c r="F1470" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
-          <t>Haen Elementary</t>
+          <t>Franklin Elementary</t>
         </is>
       </c>
       <c r="B1471" t="inlineStr">
@@ -47012,19 +47012,19 @@
       </c>
       <c r="F1471" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1472">
       <c r="A1472" t="inlineStr">
         <is>
-          <t>Omro Elementary</t>
+          <t>Westside Elementary</t>
         </is>
       </c>
       <c r="B1472" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1472" t="inlineStr">
@@ -47044,19 +47044,19 @@
       </c>
       <c r="F1472" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1473">
       <c r="A1473" t="inlineStr">
         <is>
-          <t>Gegan Elementary</t>
+          <t>Little Chute Elementary</t>
         </is>
       </c>
       <c r="B1473" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1473" t="inlineStr">
@@ -47066,29 +47066,29 @@
       </c>
       <c r="D1473" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E1473" t="inlineStr">
+        <is>
+          <t>X2N2</t>
+        </is>
+      </c>
+      <c r="F1473" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E1473" t="inlineStr">
-        <is>
-          <t>X3R2</t>
-        </is>
-      </c>
-      <c r="F1473" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
     </row>
     <row r="1474">
       <c r="A1474" t="inlineStr">
         <is>
-          <t>Huntley Elementary</t>
+          <t>Clovis Grove Elementary</t>
         </is>
       </c>
       <c r="B1474" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1474" t="inlineStr">
@@ -47108,14 +47108,14 @@
       </c>
       <c r="F1474" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1475">
       <c r="A1475" t="inlineStr">
         <is>
-          <t>Janssen Elementary</t>
+          <t>Westside Elementary</t>
         </is>
       </c>
       <c r="B1475" t="inlineStr">
@@ -47140,19 +47140,19 @@
       </c>
       <c r="F1475" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1476">
       <c r="A1476" t="inlineStr">
         <is>
-          <t>New Holstein Elementary</t>
+          <t>Berry Elementary</t>
         </is>
       </c>
       <c r="B1476" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1476" t="inlineStr">
@@ -47172,19 +47172,19 @@
       </c>
       <c r="F1476" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1477">
       <c r="A1477" t="inlineStr">
         <is>
-          <t>Roosevelt Elementary</t>
+          <t>Haen Elementary</t>
         </is>
       </c>
       <c r="B1477" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1477" t="inlineStr">
@@ -47204,14 +47204,14 @@
       </c>
       <c r="F1477" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="1478">
       <c r="A1478" t="inlineStr">
         <is>
-          <t>Wilson Elementary</t>
+          <t>Gegan Elementary</t>
         </is>
       </c>
       <c r="B1478" t="inlineStr">
@@ -47236,19 +47236,19 @@
       </c>
       <c r="F1478" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="1479">
       <c r="A1479" t="inlineStr">
         <is>
-          <t>Odyssey-Magellan</t>
+          <t>Franklin Elementary</t>
         </is>
       </c>
       <c r="B1479" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1479" t="inlineStr">
@@ -47268,19 +47268,19 @@
       </c>
       <c r="F1479" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="1480">
       <c r="A1480" t="inlineStr">
         <is>
-          <t>Clovis Grove Elementary</t>
+          <t>North Greenville Elementary</t>
         </is>
       </c>
       <c r="B1480" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1480" t="inlineStr">
@@ -47300,19 +47300,19 @@
       </c>
       <c r="F1480" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
-          <t>Read Elementary</t>
+          <t>Rock Ledge Elementary</t>
         </is>
       </c>
       <c r="B1481" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1481" t="inlineStr">
@@ -47332,14 +47332,14 @@
       </c>
       <c r="F1481" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1482">
       <c r="A1482" t="inlineStr">
         <is>
-          <t>Appleton Bilingual School</t>
+          <t>Janssen Elementary</t>
         </is>
       </c>
       <c r="B1482" t="inlineStr">
@@ -47371,12 +47371,12 @@
     <row r="1483">
       <c r="A1483" t="inlineStr">
         <is>
-          <t>Tullar Elementary</t>
+          <t>Odyssey-Magellan</t>
         </is>
       </c>
       <c r="B1483" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1483" t="inlineStr">
@@ -47396,19 +47396,19 @@
       </c>
       <c r="F1483" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1484">
       <c r="A1484" t="inlineStr">
         <is>
-          <t>Quinney Elementary</t>
+          <t>Jefferson Elementary</t>
         </is>
       </c>
       <c r="B1484" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1484" t="inlineStr">
@@ -47428,7 +47428,7 @@
       </c>
       <c r="F1484" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -47467,7 +47467,7 @@
     <row r="1486">
       <c r="A1486" t="inlineStr">
         <is>
-          <t>Edison Elementary</t>
+          <t>Badger Elementary</t>
         </is>
       </c>
       <c r="B1486" t="inlineStr">
@@ -47492,7 +47492,7 @@
       </c>
       <c r="F1486" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -47531,12 +47531,12 @@
     <row r="1488">
       <c r="A1488" t="inlineStr">
         <is>
-          <t>Butte des Morts Elementary</t>
+          <t>Quinney Elementary</t>
         </is>
       </c>
       <c r="B1488" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1488" t="inlineStr">
@@ -47556,14 +47556,14 @@
       </c>
       <c r="F1488" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="1489">
       <c r="A1489" t="inlineStr">
         <is>
-          <t>Houdini Elementary</t>
+          <t>Edison Elementary</t>
         </is>
       </c>
       <c r="B1489" t="inlineStr">
@@ -47588,19 +47588,19 @@
       </c>
       <c r="F1489" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1490">
       <c r="A1490" t="inlineStr">
         <is>
-          <t>Oaklawn Elementary</t>
+          <t>Appleton Bilingual School</t>
         </is>
       </c>
       <c r="B1490" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1490" t="inlineStr">
@@ -47620,19 +47620,19 @@
       </c>
       <c r="F1490" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
-          <t>Chilton Elementary</t>
+          <t>Tullar Elementary</t>
         </is>
       </c>
       <c r="B1491" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1491" t="inlineStr">
@@ -47652,14 +47652,14 @@
       </c>
       <c r="F1491" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="1492">
       <c r="A1492" t="inlineStr">
         <is>
-          <t>Franklin Elementary</t>
+          <t>Little Chute Elementary</t>
         </is>
       </c>
       <c r="B1492" t="inlineStr">
@@ -47684,14 +47684,14 @@
       </c>
       <c r="F1492" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1493">
       <c r="A1493" t="inlineStr">
         <is>
-          <t>Traeger Elementary</t>
+          <t>Wilson Elementary</t>
         </is>
       </c>
       <c r="B1493" t="inlineStr">
@@ -47716,19 +47716,19 @@
       </c>
       <c r="F1493" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="1494">
       <c r="A1494" t="inlineStr">
         <is>
-          <t>Jefferson Elementary</t>
+          <t>New Holstein Elementary</t>
         </is>
       </c>
       <c r="B1494" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1494" t="inlineStr">
@@ -47748,19 +47748,19 @@
       </c>
       <c r="F1494" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1495">
       <c r="A1495" t="inlineStr">
         <is>
-          <t>Ferber Elementary</t>
+          <t>Butte des Morts Elementary</t>
         </is>
       </c>
       <c r="B1495" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1495" t="inlineStr">
@@ -47780,19 +47780,19 @@
       </c>
       <c r="F1495" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1496">
       <c r="A1496" t="inlineStr">
         <is>
-          <t>Coolidge Elementary</t>
+          <t>Park Community Charter School</t>
         </is>
       </c>
       <c r="B1496" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1496" t="inlineStr">
@@ -47812,14 +47812,14 @@
       </c>
       <c r="F1496" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="1497">
       <c r="A1497" t="inlineStr">
         <is>
-          <t>Badger Elementary</t>
+          <t>Houdini Elementary</t>
         </is>
       </c>
       <c r="B1497" t="inlineStr">
@@ -47851,7 +47851,7 @@
     <row r="1498">
       <c r="A1498" t="inlineStr">
         <is>
-          <t>Shapiro STEM Academy</t>
+          <t>Roosevelt Elementary</t>
         </is>
       </c>
       <c r="B1498" t="inlineStr">
@@ -47876,19 +47876,19 @@
       </c>
       <c r="F1498" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1499">
       <c r="A1499" t="inlineStr">
         <is>
-          <t>Haen Elementary</t>
+          <t>Shapiro STEM Academy</t>
         </is>
       </c>
       <c r="B1499" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1499" t="inlineStr">
@@ -47908,19 +47908,19 @@
       </c>
       <c r="F1499" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="1500">
       <c r="A1500" t="inlineStr">
         <is>
-          <t>Franklin Elementary</t>
+          <t>Highlands Elementary</t>
         </is>
       </c>
       <c r="B1500" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1500" t="inlineStr">
@@ -47940,14 +47940,14 @@
       </c>
       <c r="F1500" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
-          <t>Spring Road Elementary</t>
+          <t>Taft Elementary</t>
         </is>
       </c>
       <c r="B1501" t="inlineStr">
@@ -47972,14 +47972,14 @@
       </c>
       <c r="F1501" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1502">
       <c r="A1502" t="inlineStr">
         <is>
-          <t>North Greenville Elementary</t>
+          <t>Huntley Elementary</t>
         </is>
       </c>
       <c r="B1502" t="inlineStr">
@@ -48036,19 +48036,19 @@
       </c>
       <c r="F1503" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1504">
       <c r="A1504" t="inlineStr">
         <is>
-          <t>Highlands Elementary</t>
+          <t>Chilton Elementary</t>
         </is>
       </c>
       <c r="B1504" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1504" t="inlineStr">
@@ -48068,19 +48068,19 @@
       </c>
       <c r="F1504" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1505">
       <c r="A1505" t="inlineStr">
         <is>
-          <t>Park Community Charter School</t>
+          <t>Oaklawn Elementary</t>
         </is>
       </c>
       <c r="B1505" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1505" t="inlineStr">
@@ -48100,14 +48100,14 @@
       </c>
       <c r="F1505" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1506">
       <c r="A1506" t="inlineStr">
         <is>
-          <t>Little Chute Elementary</t>
+          <t>Ferber Elementary</t>
         </is>
       </c>
       <c r="B1506" t="inlineStr">
@@ -48132,19 +48132,19 @@
       </c>
       <c r="F1506" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="1507">
       <c r="A1507" t="inlineStr">
         <is>
-          <t>Berry Elementary</t>
+          <t>Coolidge Elementary</t>
         </is>
       </c>
       <c r="B1507" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1507" t="inlineStr">
@@ -48171,12 +48171,12 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>Westside Elementary</t>
+          <t>Read Elementary</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1508" t="inlineStr">
@@ -48196,14 +48196,14 @@
       </c>
       <c r="F1508" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="1509">
       <c r="A1509" t="inlineStr">
         <is>
-          <t>Taft Elementary</t>
+          <t>Spring Road Elementary</t>
         </is>
       </c>
       <c r="B1509" t="inlineStr">
@@ -48228,19 +48228,19 @@
       </c>
       <c r="F1509" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1510">
       <c r="A1510" t="inlineStr">
         <is>
-          <t>Rock Ledge Elementary</t>
+          <t>Traeger Elementary</t>
         </is>
       </c>
       <c r="B1510" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1510" t="inlineStr">
@@ -48260,14 +48260,14 @@
       </c>
       <c r="F1510" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1511">
       <c r="A1511" t="inlineStr">
         <is>
-          <t>Berry Elementary</t>
+          <t>Franklin Elementary</t>
         </is>
       </c>
       <c r="B1511" t="inlineStr">
@@ -48282,12 +48282,12 @@
       </c>
       <c r="D1511" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E1511" t="inlineStr">
         <is>
-          <t>X4T2</t>
+          <t>X3R2</t>
         </is>
       </c>
       <c r="F1511" t="inlineStr">
@@ -48299,7 +48299,7 @@
     <row r="1512">
       <c r="A1512" t="inlineStr">
         <is>
-          <t>Rock Ledge Elementary</t>
+          <t>Westside Elementary</t>
         </is>
       </c>
       <c r="B1512" t="inlineStr">
@@ -48324,14 +48324,14 @@
       </c>
       <c r="F1512" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1513">
       <c r="A1513" t="inlineStr">
         <is>
-          <t>Webster Stanley Elementary</t>
+          <t>Clayton Elementary</t>
         </is>
       </c>
       <c r="B1513" t="inlineStr">
@@ -48363,12 +48363,12 @@
     <row r="1514">
       <c r="A1514" t="inlineStr">
         <is>
-          <t>Westside Elementary</t>
+          <t>Spring Road Elementary</t>
         </is>
       </c>
       <c r="B1514" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1514" t="inlineStr">
@@ -48395,12 +48395,12 @@
     <row r="1515">
       <c r="A1515" t="inlineStr">
         <is>
-          <t>Quinney Elementary</t>
+          <t>Wilson Elementary</t>
         </is>
       </c>
       <c r="B1515" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1515" t="inlineStr">
@@ -48420,19 +48420,19 @@
       </c>
       <c r="F1515" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1516">
       <c r="A1516" t="inlineStr">
         <is>
-          <t>Janssen Elementary</t>
+          <t>Shapiro STEM Academy</t>
         </is>
       </c>
       <c r="B1516" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1516" t="inlineStr">
@@ -48452,14 +48452,14 @@
       </c>
       <c r="F1516" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="1517">
       <c r="A1517" t="inlineStr">
         <is>
-          <t>Hortonville Elementary</t>
+          <t>Berry Elementary</t>
         </is>
       </c>
       <c r="B1517" t="inlineStr">
@@ -48484,19 +48484,19 @@
       </c>
       <c r="F1517" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1518">
       <c r="A1518" t="inlineStr">
         <is>
-          <t>Jefferson Elementary</t>
+          <t>Little Chute Elementary</t>
         </is>
       </c>
       <c r="B1518" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1518" t="inlineStr">
@@ -48516,19 +48516,19 @@
       </c>
       <c r="F1518" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1519">
       <c r="A1519" t="inlineStr">
         <is>
-          <t>Black Creek Elementary</t>
+          <t>Jefferson Elementary</t>
         </is>
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1519" t="inlineStr">
@@ -48548,14 +48548,14 @@
       </c>
       <c r="F1519" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="1520">
       <c r="A1520" t="inlineStr">
         <is>
-          <t>Haen Elementary</t>
+          <t>Woodland School</t>
         </is>
       </c>
       <c r="B1520" t="inlineStr">
@@ -48580,14 +48580,14 @@
       </c>
       <c r="F1520" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1521">
       <c r="A1521" t="inlineStr">
         <is>
-          <t>Wilson Elementary</t>
+          <t>Lakeside Elementary</t>
         </is>
       </c>
       <c r="B1521" t="inlineStr">
@@ -48612,19 +48612,19 @@
       </c>
       <c r="F1521" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>Omro Elementary</t>
+          <t>Franklin Elementary</t>
         </is>
       </c>
       <c r="B1522" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1522" t="inlineStr">
@@ -48644,19 +48644,19 @@
       </c>
       <c r="F1522" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>Lakeside Elementary</t>
+          <t>New Holstein Elementary</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1523" t="inlineStr">
@@ -48676,7 +48676,7 @@
       </c>
       <c r="F1523" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -48715,12 +48715,12 @@
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>E Cook Elementary</t>
+          <t>Rock Ledge Elementary</t>
         </is>
       </c>
       <c r="B1525" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1525" t="inlineStr">
@@ -48740,14 +48740,14 @@
       </c>
       <c r="F1525" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>Ronald C Dunlap Elementary School</t>
+          <t>Black Creek Elementary</t>
         </is>
       </c>
       <c r="B1526" t="inlineStr">
@@ -48779,12 +48779,12 @@
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>Little Chute Elementary</t>
+          <t>Gegan Elementary</t>
         </is>
       </c>
       <c r="B1527" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1527" t="inlineStr">
@@ -48804,19 +48804,19 @@
       </c>
       <c r="F1527" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>New Holstein Elementary</t>
+          <t>Roosevelt Elementary</t>
         </is>
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1528" t="inlineStr">
@@ -48843,7 +48843,7 @@
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>Tullar Elementary</t>
+          <t>Oakwood Elementary</t>
         </is>
       </c>
       <c r="B1529" t="inlineStr">
@@ -48868,14 +48868,14 @@
       </c>
       <c r="F1529" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>Woodland School</t>
+          <t>Quinney Elementary</t>
         </is>
       </c>
       <c r="B1530" t="inlineStr">
@@ -48900,19 +48900,19 @@
       </c>
       <c r="F1530" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>Houdini Elementary</t>
+          <t>Read Elementary</t>
         </is>
       </c>
       <c r="B1531" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1531" t="inlineStr">
@@ -48932,19 +48932,19 @@
       </c>
       <c r="F1531" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>Park Community Charter School</t>
+          <t>Omro Elementary</t>
         </is>
       </c>
       <c r="B1532" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1532" t="inlineStr">
@@ -48964,19 +48964,19 @@
       </c>
       <c r="F1532" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>Ferber Elementary</t>
+          <t>Oaklawn Elementary</t>
         </is>
       </c>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1533" t="inlineStr">
@@ -48996,14 +48996,14 @@
       </c>
       <c r="F1533" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>Traeger Elementary</t>
+          <t>E Cook Elementary</t>
         </is>
       </c>
       <c r="B1534" t="inlineStr">
@@ -49028,19 +49028,19 @@
       </c>
       <c r="F1534" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>Spring Road Elementary</t>
+          <t>Ronald C Dunlap Elementary School</t>
         </is>
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1535" t="inlineStr">
@@ -49067,12 +49067,12 @@
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>Franklin Elementary</t>
+          <t>Coolidge Elementary</t>
         </is>
       </c>
       <c r="B1536" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1536" t="inlineStr">
@@ -49092,19 +49092,19 @@
       </c>
       <c r="F1536" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>Gegan Elementary</t>
+          <t>Horizons Elementary</t>
         </is>
       </c>
       <c r="B1537" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1537" t="inlineStr">
@@ -49124,19 +49124,19 @@
       </c>
       <c r="F1537" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>Shapiro STEM Academy</t>
+          <t>Janssen Elementary</t>
         </is>
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1538" t="inlineStr">
@@ -49156,19 +49156,19 @@
       </c>
       <c r="F1538" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>Clayton Elementary</t>
+          <t>Freedom Elementary</t>
         </is>
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1539" t="inlineStr">
@@ -49195,12 +49195,12 @@
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>Coolidge Elementary</t>
+          <t>Haen Elementary</t>
         </is>
       </c>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1540" t="inlineStr">
@@ -49220,19 +49220,19 @@
       </c>
       <c r="F1540" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>Roosevelt Elementary</t>
+          <t>Huntley Elementary</t>
         </is>
       </c>
       <c r="B1541" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1541" t="inlineStr">
@@ -49252,14 +49252,14 @@
       </c>
       <c r="F1541" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>Taft Elementary</t>
+          <t>Roosevelt Elementary</t>
         </is>
       </c>
       <c r="B1542" t="inlineStr">
@@ -49284,19 +49284,19 @@
       </c>
       <c r="F1542" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>Roosevelt Elementary</t>
+          <t>Chilton Elementary</t>
         </is>
       </c>
       <c r="B1543" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1543" t="inlineStr">
@@ -49323,7 +49323,7 @@
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>Huntley Elementary</t>
+          <t>Hortonville Elementary</t>
         </is>
       </c>
       <c r="B1544" t="inlineStr">
@@ -49348,19 +49348,19 @@
       </c>
       <c r="F1544" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>Freedom Elementary</t>
+          <t>Horace Mann Middle</t>
         </is>
       </c>
       <c r="B1545" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1545" t="inlineStr">
@@ -49380,14 +49380,14 @@
       </c>
       <c r="F1545" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>Horace Mann Middle</t>
+          <t>Tullar Elementary</t>
         </is>
       </c>
       <c r="B1546" t="inlineStr">
@@ -49412,19 +49412,19 @@
       </c>
       <c r="F1546" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>Chilton Elementary</t>
+          <t>Park Community Charter School</t>
         </is>
       </c>
       <c r="B1547" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1547" t="inlineStr">
@@ -49444,19 +49444,19 @@
       </c>
       <c r="F1547" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>Oakwood Elementary</t>
+          <t>Houdini Elementary</t>
         </is>
       </c>
       <c r="B1548" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1548" t="inlineStr">
@@ -49483,7 +49483,7 @@
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>Oaklawn Elementary</t>
+          <t>Washington Elementary</t>
         </is>
       </c>
       <c r="B1549" t="inlineStr">
@@ -49508,19 +49508,19 @@
       </c>
       <c r="F1549" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>Horizons Elementary</t>
+          <t>Traeger Elementary</t>
         </is>
       </c>
       <c r="B1550" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1550" t="inlineStr">
@@ -49540,19 +49540,19 @@
       </c>
       <c r="F1550" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>Merrill Elementary</t>
+          <t>Greenville Elementary</t>
         </is>
       </c>
       <c r="B1551" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1551" t="inlineStr">
@@ -49572,14 +49572,14 @@
       </c>
       <c r="F1551" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>Washington Elementary</t>
+          <t>Taft Elementary</t>
         </is>
       </c>
       <c r="B1552" t="inlineStr">
@@ -49604,14 +49604,14 @@
       </c>
       <c r="F1552" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>Butte des Morts Elementary</t>
+          <t>Webster Stanley Elementary</t>
         </is>
       </c>
       <c r="B1553" t="inlineStr">
@@ -49636,14 +49636,14 @@
       </c>
       <c r="F1553" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>Read Elementary</t>
+          <t>Butte des Morts Elementary</t>
         </is>
       </c>
       <c r="B1554" t="inlineStr">
@@ -49668,14 +49668,14 @@
       </c>
       <c r="F1554" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>Greenville Elementary</t>
+          <t>Ferber Elementary</t>
         </is>
       </c>
       <c r="B1555" t="inlineStr">
@@ -49700,19 +49700,19 @@
       </c>
       <c r="F1555" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>Franklin Elementary</t>
+          <t>Merrill Elementary</t>
         </is>
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1556" t="inlineStr">
@@ -49722,29 +49722,29 @@
       </c>
       <c r="D1556" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E1556" t="inlineStr">
         <is>
-          <t>X5T3</t>
+          <t>X4T2</t>
         </is>
       </c>
       <c r="F1556" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>Chilton Middle</t>
+          <t>Badger Elementary</t>
         </is>
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1557" t="inlineStr">
@@ -49764,14 +49764,14 @@
       </c>
       <c r="F1557" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>Oakwood Elementary</t>
+          <t>Merrill Elementary</t>
         </is>
       </c>
       <c r="B1558" t="inlineStr">
@@ -49796,19 +49796,19 @@
       </c>
       <c r="F1558" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>Omro Elementary</t>
+          <t>Hortonville Middle</t>
         </is>
       </c>
       <c r="B1559" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1559" t="inlineStr">
@@ -49828,19 +49828,19 @@
       </c>
       <c r="F1559" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>Mapleview Intermediate</t>
+          <t>Hoover Elementary</t>
         </is>
       </c>
       <c r="B1560" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1560" t="inlineStr">
@@ -49867,12 +49867,12 @@
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>Spring Road Elementary</t>
+          <t>Huntley Elementary</t>
         </is>
       </c>
       <c r="B1561" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1561" t="inlineStr">
@@ -49899,12 +49899,12 @@
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>Rock Ledge Elementary</t>
+          <t>Jefferson Elementary</t>
         </is>
       </c>
       <c r="B1562" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1562" t="inlineStr">
@@ -49924,19 +49924,19 @@
       </c>
       <c r="F1562" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>Hilbert Middle</t>
+          <t>Ferber Elementary</t>
         </is>
       </c>
       <c r="B1563" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1563" t="inlineStr">
@@ -49956,14 +49956,14 @@
       </c>
       <c r="F1563" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>Hortonville Middle</t>
+          <t>Edison Elementary</t>
         </is>
       </c>
       <c r="B1564" t="inlineStr">
@@ -49988,14 +49988,14 @@
       </c>
       <c r="F1564" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>Greenville Middle</t>
+          <t>Franklin Elementary</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -50020,19 +50020,19 @@
       </c>
       <c r="F1565" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>Franklin Elementary</t>
+          <t>Highlands Elementary</t>
         </is>
       </c>
       <c r="B1566" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1566" t="inlineStr">
@@ -50052,14 +50052,14 @@
       </c>
       <c r="F1566" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>Oaklawn Elementary</t>
+          <t>Butte des Morts Elementary</t>
         </is>
       </c>
       <c r="B1567" t="inlineStr">
@@ -50084,14 +50084,14 @@
       </c>
       <c r="F1567" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>Lakeview Elementary</t>
+          <t>Shapiro STEM Academy</t>
         </is>
       </c>
       <c r="B1568" t="inlineStr">
@@ -50116,19 +50116,19 @@
       </c>
       <c r="F1568" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>Clayton Elementary</t>
+          <t>Rock Ledge Elementary</t>
         </is>
       </c>
       <c r="B1569" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1569" t="inlineStr">
@@ -50148,14 +50148,14 @@
       </c>
       <c r="F1569" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>Badger Elementary</t>
+          <t>Greenville Middle</t>
         </is>
       </c>
       <c r="B1570" t="inlineStr">
@@ -50187,12 +50187,12 @@
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>Coolidge Elementary</t>
+          <t>Mapleview Intermediate</t>
         </is>
       </c>
       <c r="B1571" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1571" t="inlineStr">
@@ -50212,19 +50212,19 @@
       </c>
       <c r="F1571" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>Roosevelt Elementary</t>
+          <t>Hilbert Middle</t>
         </is>
       </c>
       <c r="B1572" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1572" t="inlineStr">
@@ -50244,19 +50244,19 @@
       </c>
       <c r="F1572" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>Highlands Elementary</t>
+          <t>Clayton Elementary</t>
         </is>
       </c>
       <c r="B1573" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1573" t="inlineStr">
@@ -50276,14 +50276,14 @@
       </c>
       <c r="F1573" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>Read Elementary</t>
+          <t>Roosevelt Elementary</t>
         </is>
       </c>
       <c r="B1574" t="inlineStr">
@@ -50308,19 +50308,19 @@
       </c>
       <c r="F1574" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>Ronald C Dunlap Elementary School</t>
+          <t>Coolidge Elementary</t>
         </is>
       </c>
       <c r="B1575" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1575" t="inlineStr">
@@ -50340,19 +50340,19 @@
       </c>
       <c r="F1575" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>Huntley Elementary</t>
+          <t>Gegan Elementary</t>
         </is>
       </c>
       <c r="B1576" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1576" t="inlineStr">
@@ -50372,14 +50372,14 @@
       </c>
       <c r="F1576" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>Hoover Elementary</t>
+          <t>Franklin Elementary</t>
         </is>
       </c>
       <c r="B1577" t="inlineStr">
@@ -50404,19 +50404,19 @@
       </c>
       <c r="F1577" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>River View School</t>
+          <t>Washington Elementary</t>
         </is>
       </c>
       <c r="B1578" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1578" t="inlineStr">
@@ -50436,19 +50436,19 @@
       </c>
       <c r="F1578" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>E Cook Elementary</t>
+          <t>Ronald C Dunlap Elementary School</t>
         </is>
       </c>
       <c r="B1579" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1579" t="inlineStr">
@@ -50475,7 +50475,7 @@
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>Shapiro STEM Academy</t>
+          <t>Omro Elementary</t>
         </is>
       </c>
       <c r="B1580" t="inlineStr">
@@ -50500,19 +50500,19 @@
       </c>
       <c r="F1580" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
         <is>
-          <t>Jefferson Elementary</t>
+          <t>River View School</t>
         </is>
       </c>
       <c r="B1581" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1581" t="inlineStr">
@@ -50532,14 +50532,14 @@
       </c>
       <c r="F1581" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
         <is>
-          <t>Washington Elementary</t>
+          <t>Spring Road Elementary</t>
         </is>
       </c>
       <c r="B1582" t="inlineStr">
@@ -50564,19 +50564,19 @@
       </c>
       <c r="F1582" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
         <is>
-          <t>Merrill Elementary</t>
+          <t>Little Chute Intermediate</t>
         </is>
       </c>
       <c r="B1583" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1583" t="inlineStr">
@@ -50596,19 +50596,19 @@
       </c>
       <c r="F1583" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>Edison Elementary</t>
+          <t>Wilson Elementary</t>
         </is>
       </c>
       <c r="B1584" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1584" t="inlineStr">
@@ -50628,19 +50628,19 @@
       </c>
       <c r="F1584" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>Ferber Elementary</t>
+          <t>Webster Stanley Elementary</t>
         </is>
       </c>
       <c r="B1585" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1585" t="inlineStr">
@@ -50660,14 +50660,14 @@
       </c>
       <c r="F1585" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>Webster Stanley Elementary</t>
+          <t>Lakeside Elementary</t>
         </is>
       </c>
       <c r="B1586" t="inlineStr">
@@ -50692,19 +50692,19 @@
       </c>
       <c r="F1586" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>Gegan Elementary</t>
+          <t>Chilton Middle</t>
         </is>
       </c>
       <c r="B1587" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1587" t="inlineStr">
@@ -50724,14 +50724,14 @@
       </c>
       <c r="F1587" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>Traeger Elementary</t>
+          <t>Oakwood Elementary</t>
         </is>
       </c>
       <c r="B1588" t="inlineStr">
@@ -50756,14 +50756,14 @@
       </c>
       <c r="F1588" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>Taft Elementary</t>
+          <t>Read Elementary</t>
         </is>
       </c>
       <c r="B1589" t="inlineStr">
@@ -50788,19 +50788,19 @@
       </c>
       <c r="F1589" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>Johnston Elementary</t>
+          <t>Oaklawn Elementary</t>
         </is>
       </c>
       <c r="B1590" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1590" t="inlineStr">
@@ -50820,14 +50820,14 @@
       </c>
       <c r="F1590" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>Lakeside Elementary</t>
+          <t>Taft Elementary</t>
         </is>
       </c>
       <c r="B1591" t="inlineStr">
@@ -50852,14 +50852,14 @@
       </c>
       <c r="F1591" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>Little Chute Intermediate</t>
+          <t>Johnston Elementary</t>
         </is>
       </c>
       <c r="B1592" t="inlineStr">
@@ -50884,14 +50884,14 @@
       </c>
       <c r="F1592" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>Wilson Elementary</t>
+          <t>Traeger Elementary</t>
         </is>
       </c>
       <c r="B1593" t="inlineStr">
@@ -50916,14 +50916,14 @@
       </c>
       <c r="F1593" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>Butte des Morts Elementary</t>
+          <t>E Cook Elementary</t>
         </is>
       </c>
       <c r="B1594" t="inlineStr">
@@ -50948,19 +50948,19 @@
       </c>
       <c r="F1594" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>River View School</t>
+          <t>Lakeview Elementary</t>
         </is>
       </c>
       <c r="B1595" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1595" t="inlineStr">
@@ -50970,24 +50970,24 @@
       </c>
       <c r="D1595" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E1595" t="inlineStr">
         <is>
-          <t>X6T3</t>
+          <t>X5T3</t>
         </is>
       </c>
       <c r="F1595" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
         <is>
-          <t>Freedom Middle</t>
+          <t>Richmond Elementary</t>
         </is>
       </c>
       <c r="B1596" t="inlineStr">
@@ -51012,19 +51012,19 @@
       </c>
       <c r="F1596" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
         <is>
-          <t>McKinley Elementary</t>
+          <t>Winneconne Middle</t>
         </is>
       </c>
       <c r="B1597" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1597" t="inlineStr">
@@ -51044,14 +51044,14 @@
       </c>
       <c r="F1597" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
         <is>
-          <t>Fox West Academy</t>
+          <t>Houdini Elementary</t>
         </is>
       </c>
       <c r="B1598" t="inlineStr">
@@ -51076,19 +51076,19 @@
       </c>
       <c r="F1598" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>Horizons Elementary</t>
+          <t>Omro Middle</t>
         </is>
       </c>
       <c r="B1599" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1599" t="inlineStr">
@@ -51108,14 +51108,14 @@
       </c>
       <c r="F1599" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
         <is>
-          <t>Houdini Elementary</t>
+          <t>McKinley Elementary</t>
         </is>
       </c>
       <c r="B1600" t="inlineStr">
@@ -51140,14 +51140,14 @@
       </c>
       <c r="F1600" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
         <is>
-          <t>Jefferson Elementary</t>
+          <t>River View School</t>
         </is>
       </c>
       <c r="B1601" t="inlineStr">
@@ -51172,19 +51172,19 @@
       </c>
       <c r="F1601" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>New Holstein Middle</t>
+          <t>Horace Mann Middle</t>
         </is>
       </c>
       <c r="B1602" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1602" t="inlineStr">
@@ -51204,19 +51204,19 @@
       </c>
       <c r="F1602" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>South Park Middle</t>
+          <t>Highlands Elementary</t>
         </is>
       </c>
       <c r="B1603" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1603" t="inlineStr">
@@ -51236,14 +51236,14 @@
       </c>
       <c r="F1603" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
         <is>
-          <t>Badger Elementary</t>
+          <t>Seymour Middle</t>
         </is>
       </c>
       <c r="B1604" t="inlineStr">
@@ -51268,14 +51268,14 @@
       </c>
       <c r="F1604" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>Seymour Middle</t>
+          <t>Badger Elementary</t>
         </is>
       </c>
       <c r="B1605" t="inlineStr">
@@ -51300,14 +51300,14 @@
       </c>
       <c r="F1605" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
         <is>
-          <t>Mapleview Intermediate</t>
+          <t>Fox West Academy</t>
         </is>
       </c>
       <c r="B1606" t="inlineStr">
@@ -51332,19 +51332,19 @@
       </c>
       <c r="F1606" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>Ferber Elementary</t>
+          <t>New Holstein Middle</t>
         </is>
       </c>
       <c r="B1607" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1607" t="inlineStr">
@@ -51364,19 +51364,19 @@
       </c>
       <c r="F1607" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>Chilton Middle</t>
+          <t>Ferber Elementary</t>
         </is>
       </c>
       <c r="B1608" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1608" t="inlineStr">
@@ -51396,19 +51396,19 @@
       </c>
       <c r="F1608" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
         <is>
-          <t>Tipler Middle</t>
+          <t>Horizons Elementary</t>
         </is>
       </c>
       <c r="B1609" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1609" t="inlineStr">
@@ -51428,19 +51428,19 @@
       </c>
       <c r="F1609" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
         <is>
-          <t>Horace Mann Middle</t>
+          <t>Chilton Middle</t>
         </is>
       </c>
       <c r="B1610" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1610" t="inlineStr">
@@ -51460,14 +51460,14 @@
       </c>
       <c r="F1610" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>Richmond Elementary</t>
+          <t>Ronald C Dunlap Elementary School</t>
         </is>
       </c>
       <c r="B1611" t="inlineStr">
@@ -51492,19 +51492,19 @@
       </c>
       <c r="F1611" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
         <is>
-          <t>Winneconne Middle</t>
+          <t>Mapleview Intermediate</t>
         </is>
       </c>
       <c r="B1612" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1612" t="inlineStr">
@@ -51524,19 +51524,19 @@
       </c>
       <c r="F1612" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>Highlands Elementary</t>
+          <t>Hilbert Middle</t>
         </is>
       </c>
       <c r="B1613" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1613" t="inlineStr">
@@ -51556,19 +51556,19 @@
       </c>
       <c r="F1613" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>Hortonville Middle</t>
+          <t>Tipler Middle</t>
         </is>
       </c>
       <c r="B1614" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1614" t="inlineStr">
@@ -51588,14 +51588,14 @@
       </c>
       <c r="F1614" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>Greenville Middle</t>
+          <t>Woodland Intermediate</t>
         </is>
       </c>
       <c r="B1615" t="inlineStr">
@@ -51620,19 +51620,19 @@
       </c>
       <c r="F1615" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>Omro Middle</t>
+          <t>Freedom Middle</t>
         </is>
       </c>
       <c r="B1616" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1616" t="inlineStr">
@@ -51652,14 +51652,14 @@
       </c>
       <c r="F1616" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>Merrill Middle</t>
+          <t>South Park Middle</t>
         </is>
       </c>
       <c r="B1617" t="inlineStr">
@@ -51684,19 +51684,19 @@
       </c>
       <c r="F1617" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>Woodland Intermediate</t>
+          <t>Merrill Middle</t>
         </is>
       </c>
       <c r="B1618" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1618" t="inlineStr">
@@ -51716,19 +51716,19 @@
       </c>
       <c r="F1618" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
         <is>
-          <t>Maplewood Middle</t>
+          <t>Hortonville Middle</t>
         </is>
       </c>
       <c r="B1619" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1619" t="inlineStr">
@@ -51748,19 +51748,19 @@
       </c>
       <c r="F1619" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>Kaleidoscope Academy</t>
+          <t>Webster Stanley Middle</t>
         </is>
       </c>
       <c r="B1620" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1620" t="inlineStr">
@@ -51780,14 +51780,14 @@
       </c>
       <c r="F1620" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
         <is>
-          <t>Ronald C Dunlap Elementary School</t>
+          <t>Little Chute Intermediate</t>
         </is>
       </c>
       <c r="B1621" t="inlineStr">
@@ -51812,14 +51812,14 @@
       </c>
       <c r="F1621" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>Little Chute Intermediate</t>
+          <t>Kaleidoscope Academy</t>
         </is>
       </c>
       <c r="B1622" t="inlineStr">
@@ -51844,19 +51844,19 @@
       </c>
       <c r="F1622" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>Hilbert Middle</t>
+          <t>Maplewood Middle</t>
         </is>
       </c>
       <c r="B1623" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1623" t="inlineStr">
@@ -51876,19 +51876,19 @@
       </c>
       <c r="F1623" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>Webster Stanley Middle</t>
+          <t>Greenville Middle</t>
         </is>
       </c>
       <c r="B1624" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1624" t="inlineStr">
@@ -51908,14 +51908,14 @@
       </c>
       <c r="F1624" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
         <is>
-          <t>Little Chute Middle</t>
+          <t>Jefferson Elementary</t>
         </is>
       </c>
       <c r="B1625" t="inlineStr">
@@ -51930,29 +51930,29 @@
       </c>
       <c r="D1625" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E1625" t="inlineStr">
         <is>
-          <t>X7T2</t>
+          <t>X6T3</t>
         </is>
       </c>
       <c r="F1625" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">
         <is>
-          <t>Traeger Middle</t>
+          <t>Madison Middle</t>
         </is>
       </c>
       <c r="B1626" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1626" t="inlineStr">
@@ -51972,7 +51972,7 @@
       </c>
       <c r="F1626" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -52011,12 +52011,12 @@
     <row r="1628">
       <c r="A1628" t="inlineStr">
         <is>
-          <t>Wilson Middle</t>
+          <t>Merrill Middle</t>
         </is>
       </c>
       <c r="B1628" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1628" t="inlineStr">
@@ -52036,14 +52036,14 @@
       </c>
       <c r="F1628" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
         <is>
-          <t>Webster Stanley Middle</t>
+          <t>South Park Middle</t>
         </is>
       </c>
       <c r="B1629" t="inlineStr">
@@ -52068,7 +52068,7 @@
       </c>
       <c r="F1629" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>44</t>
         </is>
       </c>
     </row>
@@ -52107,7 +52107,7 @@
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>Gerritts Middle</t>
+          <t>Fox West Academy</t>
         </is>
       </c>
       <c r="B1631" t="inlineStr">
@@ -52132,19 +52132,19 @@
       </c>
       <c r="F1631" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>New Holstein Middle</t>
+          <t>Wilson Middle</t>
         </is>
       </c>
       <c r="B1632" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1632" t="inlineStr">
@@ -52164,14 +52164,14 @@
       </c>
       <c r="F1632" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>Einstein Middle</t>
+          <t>River View School</t>
         </is>
       </c>
       <c r="B1633" t="inlineStr">
@@ -52196,19 +52196,19 @@
       </c>
       <c r="F1633" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>Kaleidoscope Academy</t>
+          <t>Chilton Middle</t>
         </is>
       </c>
       <c r="B1634" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1634" t="inlineStr">
@@ -52228,14 +52228,14 @@
       </c>
       <c r="F1634" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
         <is>
-          <t>Winneconne Middle</t>
+          <t>Webster Stanley Middle</t>
         </is>
       </c>
       <c r="B1635" t="inlineStr">
@@ -52260,19 +52260,19 @@
       </c>
       <c r="F1635" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
-          <t>Seymour Middle</t>
+          <t>Maplewood Middle</t>
         </is>
       </c>
       <c r="B1636" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1636" t="inlineStr">
@@ -52292,19 +52292,19 @@
       </c>
       <c r="F1636" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>River View School</t>
+          <t>Winneconne Middle</t>
         </is>
       </c>
       <c r="B1637" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1637" t="inlineStr">
@@ -52324,14 +52324,14 @@
       </c>
       <c r="F1637" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
         <is>
-          <t>Fox West Academy</t>
+          <t>Kaleidoscope Academy</t>
         </is>
       </c>
       <c r="B1638" t="inlineStr">
@@ -52356,19 +52356,19 @@
       </c>
       <c r="F1638" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
         <is>
-          <t>Freedom Middle</t>
+          <t>Omro Middle</t>
         </is>
       </c>
       <c r="B1639" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1639" t="inlineStr">
@@ -52388,19 +52388,19 @@
       </c>
       <c r="F1639" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
         <is>
-          <t>Hilbert Middle</t>
+          <t>Gerritts Middle</t>
         </is>
       </c>
       <c r="B1640" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1640" t="inlineStr">
@@ -52420,19 +52420,19 @@
       </c>
       <c r="F1640" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>Omro Middle</t>
+          <t>New Holstein Middle</t>
         </is>
       </c>
       <c r="B1641" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1641" t="inlineStr">
@@ -52452,19 +52452,19 @@
       </c>
       <c r="F1641" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
         <is>
-          <t>Madison Middle</t>
+          <t>Traeger Middle</t>
         </is>
       </c>
       <c r="B1642" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1642" t="inlineStr">
@@ -52484,19 +52484,19 @@
       </c>
       <c r="F1642" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
         <is>
-          <t>South Park Middle</t>
+          <t>Einstein Middle</t>
         </is>
       </c>
       <c r="B1643" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1643" t="inlineStr">
@@ -52516,14 +52516,14 @@
       </c>
       <c r="F1643" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>Chilton Middle</t>
+          <t>Hilbert Middle</t>
         </is>
       </c>
       <c r="B1644" t="inlineStr">
@@ -52555,12 +52555,12 @@
     <row r="1645">
       <c r="A1645" t="inlineStr">
         <is>
-          <t>Hortonville Middle</t>
+          <t>Tipler Middle</t>
         </is>
       </c>
       <c r="B1645" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1645" t="inlineStr">
@@ -52580,19 +52580,19 @@
       </c>
       <c r="F1645" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="1646">
       <c r="A1646" t="inlineStr">
         <is>
-          <t>Maplewood Middle</t>
+          <t>Freedom Middle</t>
         </is>
       </c>
       <c r="B1646" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1646" t="inlineStr">
@@ -52612,19 +52612,19 @@
       </c>
       <c r="F1646" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1647">
       <c r="A1647" t="inlineStr">
         <is>
-          <t>Tipler Middle</t>
+          <t>Seymour Middle</t>
         </is>
       </c>
       <c r="B1647" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1647" t="inlineStr">
@@ -52644,19 +52644,19 @@
       </c>
       <c r="F1647" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="1648">
       <c r="A1648" t="inlineStr">
         <is>
-          <t>Merrill Middle</t>
+          <t>Hortonville Middle</t>
         </is>
       </c>
       <c r="B1648" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1648" t="inlineStr">
@@ -52676,14 +52676,14 @@
       </c>
       <c r="F1648" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="1649">
       <c r="A1649" t="inlineStr">
         <is>
-          <t>Greenville Middle</t>
+          <t>Little Chute Middle</t>
         </is>
       </c>
       <c r="B1649" t="inlineStr">
@@ -52708,14 +52708,14 @@
       </c>
       <c r="F1649" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="1650">
       <c r="A1650" t="inlineStr">
         <is>
-          <t>Little Chute Middle</t>
+          <t>Greenville Middle</t>
         </is>
       </c>
       <c r="B1650" t="inlineStr">
@@ -52730,24 +52730,24 @@
       </c>
       <c r="D1650" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E1650" t="inlineStr">
         <is>
-          <t>X8T2</t>
+          <t>X7T2</t>
         </is>
       </c>
       <c r="F1650" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
         <is>
-          <t>River View School</t>
+          <t>Madison Middle</t>
         </is>
       </c>
       <c r="B1651" t="inlineStr">
@@ -52772,19 +52772,19 @@
       </c>
       <c r="F1651" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
         <is>
-          <t>Chilton Middle</t>
+          <t>Shattuck Middle</t>
         </is>
       </c>
       <c r="B1652" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1652" t="inlineStr">
@@ -52804,19 +52804,19 @@
       </c>
       <c r="F1652" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="1653">
       <c r="A1653" t="inlineStr">
         <is>
-          <t>Greenville Middle</t>
+          <t>Winneconne Middle</t>
         </is>
       </c>
       <c r="B1653" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1653" t="inlineStr">
@@ -52836,14 +52836,14 @@
       </c>
       <c r="F1653" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
         <is>
-          <t>Einstein Middle</t>
+          <t>Little Chute Middle</t>
         </is>
       </c>
       <c r="B1654" t="inlineStr">
@@ -52868,14 +52868,14 @@
       </c>
       <c r="F1654" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
         <is>
-          <t>Winneconne Middle</t>
+          <t>Tipler Middle</t>
         </is>
       </c>
       <c r="B1655" t="inlineStr">
@@ -52900,19 +52900,19 @@
       </c>
       <c r="F1655" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="1656">
       <c r="A1656" t="inlineStr">
         <is>
-          <t>Hilbert Middle</t>
+          <t>Webster Stanley Middle</t>
         </is>
       </c>
       <c r="B1656" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1656" t="inlineStr">
@@ -52932,14 +52932,14 @@
       </c>
       <c r="F1656" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="1657">
       <c r="A1657" t="inlineStr">
         <is>
-          <t>Wilson Middle</t>
+          <t>Kaleidoscope Academy</t>
         </is>
       </c>
       <c r="B1657" t="inlineStr">
@@ -52964,19 +52964,19 @@
       </c>
       <c r="F1657" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="1658">
       <c r="A1658" t="inlineStr">
         <is>
-          <t>Freedom Middle</t>
+          <t>Hilbert Middle</t>
         </is>
       </c>
       <c r="B1658" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1658" t="inlineStr">
@@ -53003,12 +53003,12 @@
     <row r="1659">
       <c r="A1659" t="inlineStr">
         <is>
-          <t>Gerritts Middle</t>
+          <t>Chilton Middle</t>
         </is>
       </c>
       <c r="B1659" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1659" t="inlineStr">
@@ -53028,19 +53028,19 @@
       </c>
       <c r="F1659" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1660">
       <c r="A1660" t="inlineStr">
         <is>
-          <t>Brillion Middle</t>
+          <t>Maplewood Middle</t>
         </is>
       </c>
       <c r="B1660" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1660" t="inlineStr">
@@ -53060,14 +53060,14 @@
       </c>
       <c r="F1660" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="1661">
       <c r="A1661" t="inlineStr">
         <is>
-          <t>Maplewood Middle</t>
+          <t>Merrill Middle</t>
         </is>
       </c>
       <c r="B1661" t="inlineStr">
@@ -53092,19 +53092,19 @@
       </c>
       <c r="F1661" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="1662">
       <c r="A1662" t="inlineStr">
         <is>
-          <t>Seymour Middle</t>
+          <t>New Holstein Middle</t>
         </is>
       </c>
       <c r="B1662" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1662" t="inlineStr">
@@ -53124,19 +53124,19 @@
       </c>
       <c r="F1662" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="1663">
       <c r="A1663" t="inlineStr">
         <is>
-          <t>South Park Middle</t>
+          <t>Einstein Middle</t>
         </is>
       </c>
       <c r="B1663" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1663" t="inlineStr">
@@ -53156,14 +53156,14 @@
       </c>
       <c r="F1663" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="1664">
       <c r="A1664" t="inlineStr">
         <is>
-          <t>Shattuck Middle</t>
+          <t>Omro Middle</t>
         </is>
       </c>
       <c r="B1664" t="inlineStr">
@@ -53188,19 +53188,19 @@
       </c>
       <c r="F1664" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="1665">
       <c r="A1665" t="inlineStr">
         <is>
-          <t>New Holstein Middle</t>
+          <t>Greenville Middle</t>
         </is>
       </c>
       <c r="B1665" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1665" t="inlineStr">
@@ -53220,19 +53220,19 @@
       </c>
       <c r="F1665" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1666">
       <c r="A1666" t="inlineStr">
         <is>
-          <t>Merrill Middle</t>
+          <t>Seymour Middle</t>
         </is>
       </c>
       <c r="B1666" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1666" t="inlineStr">
@@ -53252,19 +53252,19 @@
       </c>
       <c r="F1666" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="1667">
       <c r="A1667" t="inlineStr">
         <is>
-          <t>Hortonville Middle</t>
+          <t>Traeger Middle</t>
         </is>
       </c>
       <c r="B1667" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1667" t="inlineStr">
@@ -53284,19 +53284,19 @@
       </c>
       <c r="F1667" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="1668">
       <c r="A1668" t="inlineStr">
         <is>
-          <t>Webster Stanley Middle</t>
+          <t>Brillion Middle</t>
         </is>
       </c>
       <c r="B1668" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1668" t="inlineStr">
@@ -53316,14 +53316,14 @@
       </c>
       <c r="F1668" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1669">
       <c r="A1669" t="inlineStr">
         <is>
-          <t>Kaleidoscope Academy</t>
+          <t>Wilson Middle</t>
         </is>
       </c>
       <c r="B1669" t="inlineStr">
@@ -53348,19 +53348,19 @@
       </c>
       <c r="F1669" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
         <is>
-          <t>Traeger Middle</t>
+          <t>Gerritts Middle</t>
         </is>
       </c>
       <c r="B1670" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1670" t="inlineStr">
@@ -53380,19 +53380,19 @@
       </c>
       <c r="F1670" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
         <is>
-          <t>Tipler Middle</t>
+          <t>Freedom Middle</t>
         </is>
       </c>
       <c r="B1671" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1671" t="inlineStr">
@@ -53412,14 +53412,14 @@
       </c>
       <c r="F1671" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1672">
       <c r="A1672" t="inlineStr">
         <is>
-          <t>Madison Middle</t>
+          <t>River View School</t>
         </is>
       </c>
       <c r="B1672" t="inlineStr">
@@ -53444,19 +53444,19 @@
       </c>
       <c r="F1672" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>61</t>
         </is>
       </c>
     </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>Omro Middle</t>
+          <t>Hortonville Middle</t>
         </is>
       </c>
       <c r="B1673" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1673" t="inlineStr">
@@ -53476,19 +53476,19 @@
       </c>
       <c r="F1673" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">
         <is>
-          <t>Little Chute Career Pathways Academy</t>
+          <t>South Park Middle</t>
         </is>
       </c>
       <c r="B1674" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1674" t="inlineStr">
@@ -53498,17 +53498,17 @@
       </c>
       <c r="D1674" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E1674" t="inlineStr">
         <is>
-          <t>X9T3</t>
+          <t>X8T2</t>
         </is>
       </c>
       <c r="F1674" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -53547,12 +53547,12 @@
     <row r="1676">
       <c r="A1676" t="inlineStr">
         <is>
-          <t>Omro High</t>
+          <t>New Holstein High</t>
         </is>
       </c>
       <c r="B1676" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1676" t="inlineStr">
@@ -53572,19 +53572,19 @@
       </c>
       <c r="F1676" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
         <is>
-          <t>Neenah High</t>
+          <t>Tesla Engineering Charter School</t>
         </is>
       </c>
       <c r="B1677" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1677" t="inlineStr">
@@ -53604,19 +53604,19 @@
       </c>
       <c r="F1677" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" t="inlineStr">
         <is>
-          <t>Chilton High</t>
+          <t>Shiocton High</t>
         </is>
       </c>
       <c r="B1678" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1678" t="inlineStr">
@@ -53636,14 +53636,14 @@
       </c>
       <c r="F1678" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" t="inlineStr">
         <is>
-          <t>West High</t>
+          <t>Omro High</t>
         </is>
       </c>
       <c r="B1679" t="inlineStr">
@@ -53668,19 +53668,19 @@
       </c>
       <c r="F1679" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
         <is>
-          <t>Brillion High</t>
+          <t>Seymour High</t>
         </is>
       </c>
       <c r="B1680" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1680" t="inlineStr">
@@ -53700,19 +53700,19 @@
       </c>
       <c r="F1680" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
         <is>
-          <t>Appleton Technical Academy</t>
+          <t>West High</t>
         </is>
       </c>
       <c r="B1681" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1681" t="inlineStr">
@@ -53732,19 +53732,19 @@
       </c>
       <c r="F1681" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>86</t>
         </is>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
         <is>
-          <t>Hortonville High</t>
+          <t>North High</t>
         </is>
       </c>
       <c r="B1682" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1682" t="inlineStr">
@@ -53764,14 +53764,14 @@
       </c>
       <c r="F1682" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>201</t>
         </is>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" t="inlineStr">
         <is>
-          <t>Tesla Engineering Charter School</t>
+          <t>West High</t>
         </is>
       </c>
       <c r="B1683" t="inlineStr">
@@ -53796,19 +53796,19 @@
       </c>
       <c r="F1683" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" t="inlineStr">
         <is>
-          <t>Seymour High</t>
+          <t>Brillion High</t>
         </is>
       </c>
       <c r="B1684" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1684" t="inlineStr">
@@ -53828,19 +53828,19 @@
       </c>
       <c r="F1684" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
         <is>
-          <t>Little Chute High</t>
+          <t>Chilton High</t>
         </is>
       </c>
       <c r="B1685" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Calumet</t>
         </is>
       </c>
       <c r="C1685" t="inlineStr">
@@ -53860,14 +53860,14 @@
       </c>
       <c r="F1685" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" t="inlineStr">
         <is>
-          <t>Kimberly High</t>
+          <t>Little Chute Career Pathways Academy</t>
         </is>
       </c>
       <c r="B1686" t="inlineStr">
@@ -53892,19 +53892,19 @@
       </c>
       <c r="F1686" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
         <is>
-          <t>North High</t>
+          <t>Kimberly High</t>
         </is>
       </c>
       <c r="B1687" t="inlineStr">
         <is>
-          <t>Winnebago</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1687" t="inlineStr">
@@ -53924,19 +53924,19 @@
       </c>
       <c r="F1687" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
         <is>
-          <t>Kaukauna High</t>
+          <t>Menasha High</t>
         </is>
       </c>
       <c r="B1688" t="inlineStr">
         <is>
-          <t>Outagamie</t>
+          <t>Winnebago</t>
         </is>
       </c>
       <c r="C1688" t="inlineStr">
@@ -53956,14 +53956,14 @@
       </c>
       <c r="F1688" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
         <is>
-          <t>East High</t>
+          <t>Little Chute High</t>
         </is>
       </c>
       <c r="B1689" t="inlineStr">
@@ -53988,14 +53988,14 @@
       </c>
       <c r="F1689" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
         <is>
-          <t>Shiocton High</t>
+          <t>Appleton Technical Academy</t>
         </is>
       </c>
       <c r="B1690" t="inlineStr">
@@ -54020,14 +54020,14 @@
       </c>
       <c r="F1690" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
         <is>
-          <t>West High</t>
+          <t>North High</t>
         </is>
       </c>
       <c r="B1691" t="inlineStr">
@@ -54052,14 +54052,14 @@
       </c>
       <c r="F1691" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
         <is>
-          <t>North High</t>
+          <t>East High</t>
         </is>
       </c>
       <c r="B1692" t="inlineStr">
@@ -54084,19 +54084,19 @@
       </c>
       <c r="F1692" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
         <is>
-          <t>New Holstein High</t>
+          <t>Hortonville High</t>
         </is>
       </c>
       <c r="B1693" t="inlineStr">
         <is>
-          <t>Calumet</t>
+          <t>Outagamie</t>
         </is>
       </c>
       <c r="C1693" t="inlineStr">
@@ -54116,14 +54116,14 @@
       </c>
       <c r="F1693" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
         <is>
-          <t>Menasha High</t>
+          <t>Neenah High</t>
         </is>
       </c>
       <c r="B1694" t="inlineStr">
@@ -54148,7 +54148,39 @@
       </c>
       <c r="F1694" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>Kaukauna High</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>Outagamie</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>Grade Level</t>
+        </is>
+      </c>
+      <c r="D1695" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E1695" t="inlineStr">
+        <is>
+          <t>X9T3</t>
+        </is>
+      </c>
+      <c r="F1695" t="inlineStr">
+        <is>
+          <t>38</t>
         </is>
       </c>
     </row>
